--- a/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4D6D589-19BB-4570-BDC0-53F1C67BD652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC6EE8F3-35D8-4C0E-B653-F8C150FAB212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5826" uniqueCount="1341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5828" uniqueCount="1341">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -841,18 +841,18 @@
     <t>solar resource -- CF class spv-USA_27 -- cost class 3</t>
   </si>
   <si>
+    <t>e_spv-USA_27_c2</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-USA_27 -- cost class 2</t>
+  </si>
+  <si>
     <t>e_spv-USA_27_c4</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-USA_27 -- cost class 4</t>
   </si>
   <si>
-    <t>e_spv-USA_27_c2</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-USA_27 -- cost class 2</t>
-  </si>
-  <si>
     <t>e_spv-USA_27_c5</t>
   </si>
   <si>
@@ -1051,18 +1051,18 @@
     <t>solar resource -- CF class spv-USA_20 -- cost class 5</t>
   </si>
   <si>
+    <t>e_spv-USA_20_c1</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-USA_20 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_spv-USA_20_c3</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-USA_20 -- cost class 3</t>
   </si>
   <si>
-    <t>e_spv-USA_20_c1</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-USA_20 -- cost class 1</t>
-  </si>
-  <si>
     <t>e_spv-USA_20_c4</t>
   </si>
   <si>
@@ -1159,18 +1159,18 @@
     <t>solar resource -- CF class spv-USA_17 -- cost class 5</t>
   </si>
   <si>
+    <t>e_spv-USA_16_c4</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-USA_16 -- cost class 4</t>
+  </si>
+  <si>
     <t>e_spv-USA_16_c3</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-USA_16 -- cost class 3</t>
   </si>
   <si>
-    <t>e_spv-USA_16_c4</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-USA_16 -- cost class 4</t>
-  </si>
-  <si>
     <t>e_spv-USA_16_c5</t>
   </si>
   <si>
@@ -1201,18 +1201,18 @@
     <t>solar resource -- CF class spv-USA_15 -- cost class 2</t>
   </si>
   <si>
+    <t>e_spv-USA_15_c1</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-USA_15 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_spv-USA_15_c4</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-USA_15 -- cost class 4</t>
   </si>
   <si>
-    <t>e_spv-USA_15_c1</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-USA_15 -- cost class 1</t>
-  </si>
-  <si>
     <t>e_spv-USA_15_c5</t>
   </si>
   <si>
@@ -1279,18 +1279,18 @@
     <t>solar resource -- CF class spv-USA_13 -- cost class 2</t>
   </si>
   <si>
+    <t>e_spv-USA_12_c1</t>
+  </si>
+  <si>
+    <t>solar resource -- CF class spv-USA_12 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_spv-USA_12_c3</t>
   </si>
   <si>
     <t>solar resource -- CF class spv-USA_12 -- cost class 3</t>
   </si>
   <si>
-    <t>e_spv-USA_12_c1</t>
-  </si>
-  <si>
-    <t>solar resource -- CF class spv-USA_12 -- cost class 1</t>
-  </si>
-  <si>
     <t>e_spv-USA_12_c5</t>
   </si>
   <si>
@@ -2074,18 +2074,18 @@
     <t>onshore wind resource -- CF class won-USA_32 -- cost class 4</t>
   </si>
   <si>
+    <t>e_won-USA_31_c1</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-USA_31 -- cost class 1</t>
+  </si>
+  <si>
     <t>e_won-USA_31_c3</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-USA_31 -- cost class 3</t>
   </si>
   <si>
-    <t>e_won-USA_31_c1</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-USA_31 -- cost class 1</t>
-  </si>
-  <si>
     <t>e_won-USA_31_c2</t>
   </si>
   <si>
@@ -2920,16 +2920,16 @@
     <t>onshore wind resource -- CF class won-USA_3 -- cost class 5</t>
   </si>
   <si>
+    <t>e_won-USA_3_c2</t>
+  </si>
+  <si>
+    <t>onshore wind resource -- CF class won-USA_3 -- cost class 2</t>
+  </si>
+  <si>
     <t>e_won-USA_3_c4</t>
   </si>
   <si>
     <t>onshore wind resource -- CF class won-USA_3 -- cost class 4</t>
-  </si>
-  <si>
-    <t>e_won-USA_3_c2</t>
-  </si>
-  <si>
-    <t>onshore wind resource -- CF class won-USA_3 -- cost class 2</t>
   </si>
   <si>
     <t>e_won-USA_3_c3</t>
@@ -5690,7 +5690,9 @@
       <c r="F8" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="str">
@@ -5726,7 +5728,9 @@
       <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="K9" s="1"/>
@@ -9008,7 +9012,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A47DE05-5A4F-40C0-A766-B144F985F5C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0859269-96E5-4EBF-BAB4-2C4C4F0CD346}">
   <dimension ref="B9:N119"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9087,10 +9091,10 @@
         <v>407</v>
       </c>
       <c r="L11">
-        <v>9.1499999999999998E-2</v>
+        <v>5.9121425162085843E-2</v>
       </c>
       <c r="M11">
-        <v>0.3176264259923125</v>
+        <v>0.31762642599231256</v>
       </c>
       <c r="N11">
         <v>3</v>
@@ -9125,7 +9129,7 @@
         <v>407</v>
       </c>
       <c r="L12">
-        <v>0.1545</v>
+        <v>0.14127169544740975</v>
       </c>
       <c r="M12">
         <v>0.31741654068003078</v>
@@ -9163,7 +9167,7 @@
         <v>407</v>
       </c>
       <c r="L13">
-        <v>6.6000000000000003E-2</v>
+        <v>3.7146173410404631E-2</v>
       </c>
       <c r="M13">
         <v>0.31677234901600781</v>
@@ -9201,7 +9205,7 @@
         <v>407</v>
       </c>
       <c r="L14">
-        <v>2.7112500000000002</v>
+        <v>2.3202109115384255</v>
       </c>
       <c r="M14">
         <v>0.3153850193126545</v>
@@ -9239,10 +9243,10 @@
         <v>407</v>
       </c>
       <c r="L15">
-        <v>1.9664999999999999</v>
+        <v>1.6876544743922035</v>
       </c>
       <c r="M15">
-        <v>0.31412193940694971</v>
+        <v>0.31412193940694977</v>
       </c>
       <c r="N15">
         <v>3</v>
@@ -9277,10 +9281,10 @@
         <v>407</v>
       </c>
       <c r="L16">
-        <v>3.2610000000000001</v>
+        <v>2.2773049743685378</v>
       </c>
       <c r="M16">
-        <v>0.30952976356733936</v>
+        <v>0.3097348859009057</v>
       </c>
       <c r="N16">
         <v>2</v>
@@ -9315,10 +9319,10 @@
         <v>407</v>
       </c>
       <c r="L17">
-        <v>3.0345</v>
+        <v>2.1849165966889239</v>
       </c>
       <c r="M17">
-        <v>0.30929817658150571</v>
+        <v>0.30959968410992111</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -9353,7 +9357,7 @@
         <v>407</v>
       </c>
       <c r="L18">
-        <v>0.51224999999999998</v>
+        <v>0.33812124675162025</v>
       </c>
       <c r="M18">
         <v>0.30734283625227971</v>
@@ -9391,7 +9395,7 @@
         <v>407</v>
       </c>
       <c r="L19">
-        <v>2.871</v>
+        <v>2.05691156603539</v>
       </c>
       <c r="M19">
         <v>0.30683094588739951</v>
@@ -9429,10 +9433,10 @@
         <v>407</v>
       </c>
       <c r="L20">
-        <v>51.1905</v>
+        <v>30.762514752391116</v>
       </c>
       <c r="M20">
-        <v>0.29854968166552093</v>
+        <v>0.2985814044082214</v>
       </c>
       <c r="N20">
         <v>1</v>
@@ -9467,10 +9471,10 @@
         <v>407</v>
       </c>
       <c r="L21">
-        <v>46.83</v>
+        <v>32.670436308883978</v>
       </c>
       <c r="M21">
-        <v>0.29761239372606707</v>
+        <v>0.29767753275896047</v>
       </c>
       <c r="N21">
         <v>3</v>
@@ -9505,10 +9509,10 @@
         <v>407</v>
       </c>
       <c r="L22">
-        <v>15.65475</v>
+        <v>11.811550612708729</v>
       </c>
       <c r="M22">
-        <v>0.29748056832201297</v>
+        <v>0.29759326156291499</v>
       </c>
       <c r="N22">
         <v>5</v>
@@ -9543,10 +9547,10 @@
         <v>407</v>
       </c>
       <c r="L23">
-        <v>33.249749999999999</v>
+        <v>23.089816012564818</v>
       </c>
       <c r="M23">
-        <v>0.29732181441096767</v>
+        <v>0.29740484016333191</v>
       </c>
       <c r="N23">
         <v>4</v>
@@ -9581,10 +9585,10 @@
         <v>407</v>
       </c>
       <c r="L24">
-        <v>51.216000000000001</v>
+        <v>33.495911410211455</v>
       </c>
       <c r="M24">
-        <v>0.29708715274638514</v>
+        <v>0.29718702088869503</v>
       </c>
       <c r="N24">
         <v>2</v>
@@ -9619,10 +9623,10 @@
         <v>407</v>
       </c>
       <c r="L25">
-        <v>191.78025</v>
+        <v>130.11049328136002</v>
       </c>
       <c r="M25">
-        <v>0.29069363593817976</v>
+        <v>0.29061086444469175</v>
       </c>
       <c r="N25">
         <v>3</v>
@@ -9657,10 +9661,10 @@
         <v>407</v>
       </c>
       <c r="L26">
-        <v>149.06100000000001</v>
+        <v>105.27146079744705</v>
       </c>
       <c r="M26">
-        <v>0.2901763240299563</v>
+        <v>0.29016297384417145</v>
       </c>
       <c r="N26">
         <v>4</v>
@@ -9695,10 +9699,10 @@
         <v>407</v>
       </c>
       <c r="L27">
-        <v>235.18799999999999</v>
+        <v>161.44879160312183</v>
       </c>
       <c r="M27">
-        <v>0.28950202449632212</v>
+        <v>0.28957400890507873</v>
       </c>
       <c r="N27">
         <v>2</v>
@@ -9733,10 +9737,10 @@
         <v>407</v>
       </c>
       <c r="L28">
-        <v>266.02274999999997</v>
+        <v>176.58075949876067</v>
       </c>
       <c r="M28">
-        <v>0.28895900403428726</v>
+        <v>0.28885859636434158</v>
       </c>
       <c r="N28">
         <v>1</v>
@@ -9771,10 +9775,10 @@
         <v>407</v>
       </c>
       <c r="L29">
-        <v>132.19575</v>
+        <v>103.57396815186642</v>
       </c>
       <c r="M29">
-        <v>0.28814254606308665</v>
+        <v>0.28830543526818808</v>
       </c>
       <c r="N29">
         <v>5</v>
@@ -9809,10 +9813,10 @@
         <v>407</v>
       </c>
       <c r="L30">
-        <v>296.34224999999998</v>
+        <v>230.53265520317859</v>
       </c>
       <c r="M30">
-        <v>0.28165303534803821</v>
+        <v>0.28141742775700385</v>
       </c>
       <c r="N30">
         <v>1</v>
@@ -9847,10 +9851,10 @@
         <v>407</v>
       </c>
       <c r="L31">
-        <v>167.55074999999999</v>
+        <v>120.92644538679254</v>
       </c>
       <c r="M31">
-        <v>0.28086983992869208</v>
+        <v>0.28099658483459528</v>
       </c>
       <c r="N31">
         <v>3</v>
@@ -9885,10 +9889,10 @@
         <v>407</v>
       </c>
       <c r="L32">
-        <v>236.95650000000001</v>
+        <v>151.05345657351589</v>
       </c>
       <c r="M32">
-        <v>0.27971358483935255</v>
+        <v>0.28008438831856136</v>
       </c>
       <c r="N32">
         <v>2</v>
@@ -9923,10 +9927,10 @@
         <v>407</v>
       </c>
       <c r="L33">
-        <v>202.40025</v>
+        <v>135.64862740226019</v>
       </c>
       <c r="M33">
-        <v>0.27874394911364786</v>
+        <v>0.27888482110403318</v>
       </c>
       <c r="N33">
         <v>4</v>
@@ -9961,10 +9965,10 @@
         <v>407</v>
       </c>
       <c r="L34">
-        <v>141.75749999999999</v>
+        <v>96.687766675848735</v>
       </c>
       <c r="M34">
-        <v>0.27795491444796699</v>
+        <v>0.27810771944731133</v>
       </c>
       <c r="N34">
         <v>5</v>
@@ -9999,10 +10003,10 @@
         <v>407</v>
       </c>
       <c r="L35">
-        <v>177.10050000000001</v>
+        <v>93.370207201877619</v>
       </c>
       <c r="M35">
-        <v>0.27118990187695269</v>
+        <v>0.27119754782846162</v>
       </c>
       <c r="N35">
         <v>1</v>
@@ -10037,10 +10041,10 @@
         <v>407</v>
       </c>
       <c r="L36">
-        <v>119.538</v>
+        <v>73.3340678192544</v>
       </c>
       <c r="M36">
-        <v>0.27103890867005015</v>
+        <v>0.27083391600040618</v>
       </c>
       <c r="N36">
         <v>3</v>
@@ -10075,13 +10079,13 @@
         <v>407</v>
       </c>
       <c r="L37">
-        <v>116.08425</v>
+        <v>84.496866658491697</v>
       </c>
       <c r="M37">
-        <v>0.27092879939064024</v>
+        <v>0.27079561278462438</v>
       </c>
       <c r="N37">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="2:14">
@@ -10113,13 +10117,13 @@
         <v>407</v>
       </c>
       <c r="L38">
-        <v>155.56950000000001</v>
+        <v>67.312302699004917</v>
       </c>
       <c r="M38">
-        <v>0.27050436108240639</v>
+        <v>0.27065660603237612</v>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="2:14">
@@ -10151,10 +10155,10 @@
         <v>407</v>
       </c>
       <c r="L39">
-        <v>121.5675</v>
+        <v>74.250243401435128</v>
       </c>
       <c r="M39">
-        <v>0.26901606625260999</v>
+        <v>0.26899680175724183</v>
       </c>
       <c r="N39">
         <v>5</v>
@@ -10189,10 +10193,10 @@
         <v>407</v>
       </c>
       <c r="L40">
-        <v>119.27925</v>
+        <v>56.70785777167913</v>
       </c>
       <c r="M40">
-        <v>0.26131031318222075</v>
+        <v>0.26140050417504024</v>
       </c>
       <c r="N40">
         <v>1</v>
@@ -10227,10 +10231,10 @@
         <v>407</v>
       </c>
       <c r="L41">
-        <v>88.788749999999993</v>
+        <v>52.764459685433401</v>
       </c>
       <c r="M41">
-        <v>0.260080677807845</v>
+        <v>0.26020597050723726</v>
       </c>
       <c r="N41">
         <v>4</v>
@@ -10265,10 +10269,10 @@
         <v>407</v>
       </c>
       <c r="L42">
-        <v>101.28825000000001</v>
+        <v>56.043886893425423</v>
       </c>
       <c r="M42">
-        <v>0.25965284865974619</v>
+        <v>0.25979510076462214</v>
       </c>
       <c r="N42">
         <v>3</v>
@@ -10303,10 +10307,10 @@
         <v>407</v>
       </c>
       <c r="L43">
-        <v>77.479500000000002</v>
+        <v>39.35628328034786</v>
       </c>
       <c r="M43">
-        <v>0.25925584929933693</v>
+        <v>0.25932197605343654</v>
       </c>
       <c r="N43">
         <v>2</v>
@@ -10341,10 +10345,10 @@
         <v>407</v>
       </c>
       <c r="L44">
-        <v>68.694000000000003</v>
+        <v>38.414091109958932</v>
       </c>
       <c r="M44">
-        <v>0.25918064449208655</v>
+        <v>0.25911879895617468</v>
       </c>
       <c r="N44">
         <v>5</v>
@@ -10379,10 +10383,10 @@
         <v>407</v>
       </c>
       <c r="L45">
-        <v>128.83199999999999</v>
+        <v>56.658862960546642</v>
       </c>
       <c r="M45">
-        <v>0.25023108136186678</v>
+        <v>0.25022841348249236</v>
       </c>
       <c r="N45">
         <v>1</v>
@@ -10417,10 +10421,10 @@
         <v>407</v>
       </c>
       <c r="L46">
-        <v>64.600499999999997</v>
+        <v>37.436678126793737</v>
       </c>
       <c r="M46">
-        <v>0.25000232139285344</v>
+        <v>0.25020798120344173</v>
       </c>
       <c r="N46">
         <v>4</v>
@@ -10455,10 +10459,10 @@
         <v>407</v>
       </c>
       <c r="L47">
-        <v>121.48125</v>
+        <v>55.518317682969979</v>
       </c>
       <c r="M47">
-        <v>0.24951494886626682</v>
+        <v>0.24984368168520524</v>
       </c>
       <c r="N47">
         <v>3</v>
@@ -10493,10 +10497,10 @@
         <v>407</v>
       </c>
       <c r="L48">
-        <v>20.166</v>
+        <v>12.402090768144227</v>
       </c>
       <c r="M48">
-        <v>0.24947336444453641</v>
+        <v>0.24977386057981746</v>
       </c>
       <c r="N48">
         <v>5</v>
@@ -10531,10 +10535,10 @@
         <v>407</v>
       </c>
       <c r="L49">
-        <v>76.345500000000001</v>
+        <v>32.542695742002358</v>
       </c>
       <c r="M49">
-        <v>0.24915834831953049</v>
+        <v>0.24922358884274651</v>
       </c>
       <c r="N49">
         <v>2</v>
@@ -10569,10 +10573,10 @@
         <v>407</v>
       </c>
       <c r="L50">
-        <v>121.82850000000001</v>
+        <v>51.221677188442776</v>
       </c>
       <c r="M50">
-        <v>0.24028491774975264</v>
+        <v>0.24036881927631074</v>
       </c>
       <c r="N50">
         <v>3</v>
@@ -10607,10 +10611,10 @@
         <v>407</v>
       </c>
       <c r="L51">
-        <v>76.132499999999993</v>
+        <v>32.915931695239301</v>
       </c>
       <c r="M51">
-        <v>0.24024801805075435</v>
+        <v>0.24025433445219246</v>
       </c>
       <c r="N51">
         <v>1</v>
@@ -10645,10 +10649,10 @@
         <v>407</v>
       </c>
       <c r="L52">
-        <v>96.005250000000004</v>
+        <v>40.04287703521166</v>
       </c>
       <c r="M52">
-        <v>0.23974497863200583</v>
+        <v>0.2397639313428401</v>
       </c>
       <c r="N52">
         <v>2</v>
@@ -10683,10 +10687,10 @@
         <v>407</v>
       </c>
       <c r="L53">
-        <v>24.356249999999999</v>
+        <v>14.28143314597758</v>
       </c>
       <c r="M53">
-        <v>0.23901180664627436</v>
+        <v>0.23922474398899321</v>
       </c>
       <c r="N53">
         <v>5</v>
@@ -10721,10 +10725,10 @@
         <v>407</v>
       </c>
       <c r="L54">
-        <v>59.15475</v>
+        <v>29.344430292812255</v>
       </c>
       <c r="M54">
-        <v>0.23854335740945368</v>
+        <v>0.23884532206360004</v>
       </c>
       <c r="N54">
         <v>4</v>
@@ -10759,10 +10763,10 @@
         <v>407</v>
       </c>
       <c r="L55">
-        <v>180.96449999999999</v>
+        <v>72.4694333480941</v>
       </c>
       <c r="M55">
-        <v>0.2300873228837351</v>
+        <v>0.23013779352098374</v>
       </c>
       <c r="N55">
         <v>2</v>
@@ -10797,10 +10801,10 @@
         <v>407</v>
       </c>
       <c r="L56">
-        <v>145.55549999999999</v>
+        <v>63.019439708758881</v>
       </c>
       <c r="M56">
-        <v>0.23002495990649821</v>
+        <v>0.22991791730070382</v>
       </c>
       <c r="N56">
         <v>1</v>
@@ -10835,10 +10839,10 @@
         <v>407</v>
       </c>
       <c r="L57">
-        <v>188.46225000000001</v>
+        <v>79.792362289799939</v>
       </c>
       <c r="M57">
-        <v>0.22907385635941735</v>
+        <v>0.22913702912619313</v>
       </c>
       <c r="N57">
         <v>3</v>
@@ -10873,10 +10877,10 @@
         <v>407</v>
       </c>
       <c r="L58">
-        <v>144.26400000000001</v>
+        <v>64.750284541025749</v>
       </c>
       <c r="M58">
-        <v>0.22894861514343393</v>
+        <v>0.22904821229235756</v>
       </c>
       <c r="N58">
         <v>4</v>
@@ -10911,10 +10915,10 @@
         <v>407</v>
       </c>
       <c r="L59">
-        <v>74.808000000000007</v>
+        <v>38.237723330350633</v>
       </c>
       <c r="M59">
-        <v>0.22832634931871698</v>
+        <v>0.22855446043792102</v>
       </c>
       <c r="N59">
         <v>5</v>
@@ -10949,10 +10953,10 @@
         <v>407</v>
       </c>
       <c r="L60">
-        <v>178.917</v>
+        <v>86.203681686832965</v>
       </c>
       <c r="M60">
-        <v>0.22099829274453281</v>
+        <v>0.2207242647255758</v>
       </c>
       <c r="N60">
         <v>1</v>
@@ -10987,10 +10991,10 @@
         <v>407</v>
       </c>
       <c r="L61">
-        <v>126.06375</v>
+        <v>53.383109075725955</v>
       </c>
       <c r="M61">
-        <v>0.22036891442278153</v>
+        <v>0.22019326244600554</v>
       </c>
       <c r="N61">
         <v>3</v>
@@ -11025,10 +11029,10 @@
         <v>407</v>
       </c>
       <c r="L62">
-        <v>107.60475</v>
+        <v>45.432934454727928</v>
       </c>
       <c r="M62">
-        <v>0.22012740794475832</v>
+        <v>0.22009137336102919</v>
       </c>
       <c r="N62">
         <v>4</v>
@@ -11063,10 +11067,10 @@
         <v>407</v>
       </c>
       <c r="L63">
-        <v>139.83150000000001</v>
+        <v>62.112968249450788</v>
       </c>
       <c r="M63">
-        <v>0.21991307783611855</v>
+        <v>0.21971126459878354</v>
       </c>
       <c r="N63">
         <v>2</v>
@@ -11101,10 +11105,10 @@
         <v>407</v>
       </c>
       <c r="L64">
-        <v>43.459499999999998</v>
+        <v>22.491946816846291</v>
       </c>
       <c r="M64">
-        <v>0.21953281244451053</v>
+        <v>0.21950972875985331</v>
       </c>
       <c r="N64">
         <v>5</v>
@@ -11139,10 +11143,10 @@
         <v>407</v>
       </c>
       <c r="L65">
-        <v>261.74324999999999</v>
+        <v>165.48505841899595</v>
       </c>
       <c r="M65">
-        <v>0.21078197976824711</v>
+        <v>0.21028317715416303</v>
       </c>
       <c r="N65">
         <v>1</v>
@@ -11177,10 +11181,10 @@
         <v>407</v>
       </c>
       <c r="L66">
-        <v>183.34575000000001</v>
+        <v>103.38881245099651</v>
       </c>
       <c r="M66">
-        <v>0.21062461674881428</v>
+        <v>0.21025826839477962</v>
       </c>
       <c r="N66">
         <v>2</v>
@@ -11215,10 +11219,10 @@
         <v>407</v>
       </c>
       <c r="L67">
-        <v>174.20849999999999</v>
+        <v>100.88681146926407</v>
       </c>
       <c r="M67">
-        <v>0.20921336288701795</v>
+        <v>0.20891600971493565</v>
       </c>
       <c r="N67">
         <v>3</v>
@@ -11253,10 +11257,10 @@
         <v>407</v>
       </c>
       <c r="L68">
-        <v>157.7355</v>
+        <v>112.24257950005698</v>
       </c>
       <c r="M68">
-        <v>0.20812844218521354</v>
+        <v>0.2076927789546569</v>
       </c>
       <c r="N68">
         <v>4</v>
@@ -11291,10 +11295,10 @@
         <v>407</v>
       </c>
       <c r="L69">
-        <v>94.726500000000001</v>
+        <v>75.030811308375007</v>
       </c>
       <c r="M69">
-        <v>0.2079683688988325</v>
+        <v>0.20754984987632363</v>
       </c>
       <c r="N69">
         <v>5</v>
@@ -11329,10 +11333,10 @@
         <v>407</v>
       </c>
       <c r="L70">
-        <v>182.91524999999999</v>
+        <v>136.82577471225494</v>
       </c>
       <c r="M70">
-        <v>0.20056435602560341</v>
+        <v>0.20046825103685054</v>
       </c>
       <c r="N70">
         <v>2</v>
@@ -11367,10 +11371,10 @@
         <v>407</v>
       </c>
       <c r="L71">
-        <v>452.54700000000003</v>
+        <v>435.35334445415674</v>
       </c>
       <c r="M71">
-        <v>0.20006290130284163</v>
+        <v>0.2001264667496748</v>
       </c>
       <c r="N71">
         <v>5</v>
@@ -11405,13 +11409,13 @@
         <v>407</v>
       </c>
       <c r="L72">
-        <v>179.70824999999999</v>
+        <v>107.67731858789318</v>
       </c>
       <c r="M72">
-        <v>0.19927824760004004</v>
+        <v>0.19938180831234223</v>
       </c>
       <c r="N72">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="2:14">
@@ -11443,13 +11447,13 @@
         <v>407</v>
       </c>
       <c r="L73">
-        <v>142.47524999999999</v>
+        <v>137.81584504225768</v>
       </c>
       <c r="M73">
-        <v>0.19921568692319658</v>
+        <v>0.1992819067642049</v>
       </c>
       <c r="N73">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="2:14">
@@ -11481,10 +11485,10 @@
         <v>407</v>
       </c>
       <c r="L74">
-        <v>187.55099999999999</v>
+        <v>136.8437629844295</v>
       </c>
       <c r="M74">
-        <v>0.19865786713714848</v>
+        <v>0.19871894541711382</v>
       </c>
       <c r="N74">
         <v>4</v>
@@ -11519,10 +11523,10 @@
         <v>407</v>
       </c>
       <c r="L75">
-        <v>127.71599999999999</v>
+        <v>91.20965378884047</v>
       </c>
       <c r="M75">
-        <v>0.19312213988862284</v>
+        <v>0.19314163885297322</v>
       </c>
       <c r="N75">
         <v>1</v>
@@ -11557,10 +11561,10 @@
         <v>407</v>
       </c>
       <c r="L76">
-        <v>181.40549999999999</v>
+        <v>152.82760741146646</v>
       </c>
       <c r="M76">
-        <v>0.1912971233714269</v>
+        <v>0.19117019039477959</v>
       </c>
       <c r="N76">
         <v>2</v>
@@ -11595,10 +11599,10 @@
         <v>407</v>
       </c>
       <c r="L77">
-        <v>202.61324999999999</v>
+        <v>186.89457580865286</v>
       </c>
       <c r="M77">
-        <v>0.19073286787736207</v>
+        <v>0.1908296411580136</v>
       </c>
       <c r="N77">
         <v>5</v>
@@ -11633,10 +11637,10 @@
         <v>407</v>
       </c>
       <c r="L78">
-        <v>195.792</v>
+        <v>183.25206674609208</v>
       </c>
       <c r="M78">
-        <v>0.19070183322873691</v>
+        <v>0.19067767475309977</v>
       </c>
       <c r="N78">
         <v>3</v>
@@ -11671,10 +11675,10 @@
         <v>407</v>
       </c>
       <c r="L79">
-        <v>151.82474999999999</v>
+        <v>128.52978972225083</v>
       </c>
       <c r="M79">
-        <v>0.18939634057369595</v>
+        <v>0.1893801525334507</v>
       </c>
       <c r="N79">
         <v>4</v>
@@ -11709,10 +11713,10 @@
         <v>407</v>
       </c>
       <c r="L80">
-        <v>67.129499999999993</v>
+        <v>64.104416326370327</v>
       </c>
       <c r="M80">
-        <v>0.18321508598029407</v>
+        <v>0.18320583758965836</v>
       </c>
       <c r="N80">
         <v>1</v>
@@ -11747,10 +11751,10 @@
         <v>407</v>
       </c>
       <c r="L81">
-        <v>55.424999999999997</v>
+        <v>50.123902385820259</v>
       </c>
       <c r="M81">
-        <v>0.18160311590512784</v>
+        <v>0.18157679961047363</v>
       </c>
       <c r="N81">
         <v>2</v>
@@ -11785,10 +11789,10 @@
         <v>407</v>
       </c>
       <c r="L82">
-        <v>41.847000000000001</v>
+        <v>35.426473840181913</v>
       </c>
       <c r="M82">
-        <v>0.18150856422435815</v>
+        <v>0.18146447443654232</v>
       </c>
       <c r="N82">
         <v>3</v>
@@ -11823,10 +11827,10 @@
         <v>407</v>
       </c>
       <c r="L83">
-        <v>47.698500000000003</v>
+        <v>42.422242991035532</v>
       </c>
       <c r="M83">
-        <v>0.18103305700921657</v>
+        <v>0.18094173616697556</v>
       </c>
       <c r="N83">
         <v>4</v>
@@ -11861,10 +11865,10 @@
         <v>407</v>
       </c>
       <c r="L84">
-        <v>34.401000000000003</v>
+        <v>30.965071809377516</v>
       </c>
       <c r="M84">
-        <v>0.1797413494885895</v>
+        <v>0.17953907210744299</v>
       </c>
       <c r="N84">
         <v>5</v>
@@ -11899,10 +11903,10 @@
         <v>407</v>
       </c>
       <c r="L85">
-        <v>2.76</v>
+        <v>1.7531559017439071</v>
       </c>
       <c r="M85">
-        <v>0.17104115260726924</v>
+        <v>0.17094838670800025</v>
       </c>
       <c r="N85">
         <v>1</v>
@@ -11937,10 +11941,10 @@
         <v>407</v>
       </c>
       <c r="L86">
-        <v>0.4995</v>
+        <v>0.41021156703776129</v>
       </c>
       <c r="M86">
-        <v>0.17089449341939869</v>
+        <v>0.17089250950427837</v>
       </c>
       <c r="N86">
         <v>4</v>
@@ -11975,10 +11979,10 @@
         <v>407</v>
       </c>
       <c r="L87">
-        <v>1.4137500000000001</v>
+        <v>1.2215484562336485</v>
       </c>
       <c r="M87">
-        <v>0.17056133955837946</v>
+        <v>0.17085267657873843</v>
       </c>
       <c r="N87">
         <v>3</v>
@@ -12013,10 +12017,10 @@
         <v>407</v>
       </c>
       <c r="L88">
-        <v>5.7127499999999998</v>
+        <v>5.1154075570897133</v>
       </c>
       <c r="M88">
-        <v>0.17019467827152451</v>
+        <v>0.17021495777567625</v>
       </c>
       <c r="N88">
         <v>2</v>
@@ -12051,10 +12055,10 @@
         <v>407</v>
       </c>
       <c r="L89">
-        <v>0.53549999999999998</v>
+        <v>0.39655739854338756</v>
       </c>
       <c r="M89">
-        <v>0.16760754764296981</v>
+        <v>0.1677425130664888</v>
       </c>
       <c r="N89">
         <v>5</v>
@@ -12089,13 +12093,13 @@
         <v>407</v>
       </c>
       <c r="L90">
-        <v>3.9082499999999998</v>
+        <v>7.2024772814328467E-2</v>
       </c>
       <c r="M90">
-        <v>0.15915688788690277</v>
+        <v>0.15912146140568298</v>
       </c>
       <c r="N90">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91" spans="2:14">
@@ -12127,13 +12131,13 @@
         <v>407</v>
       </c>
       <c r="L91">
-        <v>0.20175000000000001</v>
+        <v>1.340197232550195</v>
       </c>
       <c r="M91">
-        <v>0.1591136194670506</v>
+        <v>0.15905545476541275</v>
       </c>
       <c r="N91">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="2:14">
@@ -12165,10 +12169,10 @@
         <v>407</v>
       </c>
       <c r="L92">
-        <v>6.9000000000000006E-2</v>
+        <v>2.4946999508195643E-2</v>
       </c>
       <c r="M92">
-        <v>0.15867976916421064</v>
+        <v>0.15887529830663763</v>
       </c>
       <c r="N92">
         <v>5</v>
@@ -12203,10 +12207,10 @@
         <v>407</v>
       </c>
       <c r="L93">
-        <v>1.9237500000000001</v>
+        <v>0.72218023182605595</v>
       </c>
       <c r="M93">
-        <v>0.1572501387854989</v>
+        <v>0.15713341550647492</v>
       </c>
       <c r="N93">
         <v>1</v>
@@ -12241,10 +12245,10 @@
         <v>407</v>
       </c>
       <c r="L94">
-        <v>2.4180000000000001</v>
+        <v>0.84332714042120538</v>
       </c>
       <c r="M94">
-        <v>0.15685121359419457</v>
+        <v>0.15676307115023017</v>
       </c>
       <c r="N94">
         <v>2</v>
@@ -12279,10 +12283,10 @@
         <v>407</v>
       </c>
       <c r="L95">
-        <v>12.117000000000001</v>
+        <v>4.7852344306976109</v>
       </c>
       <c r="M95">
-        <v>0.15179338283189953</v>
+        <v>0.15171081020278171</v>
       </c>
       <c r="N95">
         <v>3</v>
@@ -12317,10 +12321,10 @@
         <v>407</v>
       </c>
       <c r="L96">
-        <v>17.35425</v>
+        <v>6.3561841509281667</v>
       </c>
       <c r="M96">
-        <v>0.15117222029081151</v>
+        <v>0.1513195907091136</v>
       </c>
       <c r="N96">
         <v>2</v>
@@ -12355,13 +12359,13 @@
         <v>407</v>
       </c>
       <c r="L97">
-        <v>9.9457500000000003</v>
+        <v>3.5895754590867393</v>
       </c>
       <c r="M97">
-        <v>0.14920028228910609</v>
+        <v>0.14950003839101228</v>
       </c>
       <c r="N97">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="2:14">
@@ -12393,13 +12397,13 @@
         <v>407</v>
       </c>
       <c r="L98">
-        <v>10.46625</v>
+        <v>3.19230767756325</v>
       </c>
       <c r="M98">
-        <v>0.14919574463292082</v>
+        <v>0.14930654321157202</v>
       </c>
       <c r="N98">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99" spans="2:14">
@@ -12431,10 +12435,10 @@
         <v>407</v>
       </c>
       <c r="L99">
-        <v>11.99325</v>
+        <v>4.3646392764263444</v>
       </c>
       <c r="M99">
-        <v>0.14722370240670113</v>
+        <v>0.14735803508009113</v>
       </c>
       <c r="N99">
         <v>5</v>
@@ -12469,10 +12473,10 @@
         <v>407</v>
       </c>
       <c r="L100">
-        <v>17.346</v>
+        <v>12.220085077748612</v>
       </c>
       <c r="M100">
-        <v>0.14222014212467599</v>
+        <v>0.14200953821172521</v>
       </c>
       <c r="N100">
         <v>3</v>
@@ -12507,10 +12511,10 @@
         <v>407</v>
       </c>
       <c r="L101">
-        <v>7.6522500000000004</v>
+        <v>2.4710754540088598</v>
       </c>
       <c r="M101">
-        <v>0.14115770707722786</v>
+        <v>0.14114566171370291</v>
       </c>
       <c r="N101">
         <v>2</v>
@@ -12545,10 +12549,10 @@
         <v>407</v>
       </c>
       <c r="L102">
-        <v>13.752000000000001</v>
+        <v>5.8535236545697735</v>
       </c>
       <c r="M102">
-        <v>0.14101641112265148</v>
+        <v>0.14080505602257928</v>
       </c>
       <c r="N102">
         <v>4</v>
@@ -12583,10 +12587,10 @@
         <v>407</v>
       </c>
       <c r="L103">
-        <v>17.377500000000001</v>
+        <v>7.268488719978639</v>
       </c>
       <c r="M103">
-        <v>0.13920580059074292</v>
+        <v>0.1390199228502618</v>
       </c>
       <c r="N103">
         <v>5</v>
@@ -12621,10 +12625,10 @@
         <v>407</v>
       </c>
       <c r="L104">
-        <v>5.2177499999999997</v>
+        <v>1.6319614928599271</v>
       </c>
       <c r="M104">
-        <v>0.13850685783864025</v>
+        <v>0.13858615603268049</v>
       </c>
       <c r="N104">
         <v>1</v>
@@ -12659,10 +12663,10 @@
         <v>407</v>
       </c>
       <c r="L105">
-        <v>11.25675</v>
+        <v>4.3512213940656812</v>
       </c>
       <c r="M105">
-        <v>0.13199249821713696</v>
+        <v>0.13225653336710261</v>
       </c>
       <c r="N105">
         <v>4</v>
@@ -12697,10 +12701,10 @@
         <v>407</v>
       </c>
       <c r="L106">
-        <v>0.81374999999999997</v>
+        <v>0.25840837819858364</v>
       </c>
       <c r="M106">
-        <v>0.13130563626767663</v>
+        <v>0.13139209076141431</v>
       </c>
       <c r="N106">
         <v>3</v>
@@ -12735,10 +12739,10 @@
         <v>407</v>
       </c>
       <c r="L107">
-        <v>15.066000000000001</v>
+        <v>6.2281632192383976</v>
       </c>
       <c r="M107">
-        <v>0.13042038649274498</v>
+        <v>0.13117452799968032</v>
       </c>
       <c r="N107">
         <v>5</v>
@@ -12773,10 +12777,10 @@
         <v>407</v>
       </c>
       <c r="L108">
-        <v>2.40225</v>
+        <v>1.5670302748617806</v>
       </c>
       <c r="M108">
-        <v>0.13020524429459274</v>
+        <v>0.12993121692651699</v>
       </c>
       <c r="N108">
         <v>1</v>
@@ -12811,10 +12815,10 @@
         <v>407</v>
       </c>
       <c r="L109">
-        <v>0.86775000000000002</v>
+        <v>0.56248365545525125</v>
       </c>
       <c r="M109">
-        <v>0.12872142662215072</v>
+        <v>0.12826581350650726</v>
       </c>
       <c r="N109">
         <v>2</v>
@@ -12849,13 +12853,13 @@
         <v>407</v>
       </c>
       <c r="L110">
-        <v>5.7817499999999997</v>
+        <v>0.5949822801028356</v>
       </c>
       <c r="M110">
-        <v>0.12133592060925101</v>
+        <v>0.12162313111682184</v>
       </c>
       <c r="N110">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="2:14">
@@ -12887,13 +12891,13 @@
         <v>407</v>
       </c>
       <c r="L111">
-        <v>1.83525</v>
+        <v>1.7421297197329144</v>
       </c>
       <c r="M111">
-        <v>0.12113479370644779</v>
+        <v>0.12135613714756602</v>
       </c>
       <c r="N111">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="2:14">
@@ -12925,10 +12929,10 @@
         <v>407</v>
       </c>
       <c r="L112">
-        <v>4.4437499999999996</v>
+        <v>1.1465425899557093</v>
       </c>
       <c r="M112">
-        <v>0.12110365901739706</v>
+        <v>0.12109581877668864</v>
       </c>
       <c r="N112">
         <v>5</v>
@@ -12963,10 +12967,10 @@
         <v>407</v>
       </c>
       <c r="L113">
-        <v>2.0362499999999999</v>
+        <v>0.56887616879594249</v>
       </c>
       <c r="M113">
-        <v>0.11929038115397567</v>
+        <v>0.11923597738331916</v>
       </c>
       <c r="N113">
         <v>2</v>
@@ -13001,10 +13005,10 @@
         <v>407</v>
       </c>
       <c r="L114">
-        <v>4.4400000000000004</v>
+        <v>1.523174277285682</v>
       </c>
       <c r="M114">
-        <v>0.11864944340775302</v>
+        <v>0.11886129287738087</v>
       </c>
       <c r="N114">
         <v>4</v>
@@ -13039,7 +13043,7 @@
         <v>407</v>
       </c>
       <c r="L115">
-        <v>0.83250000000000002</v>
+        <v>0.19882591925441517</v>
       </c>
       <c r="M115">
         <v>0.1146139277839343</v>
@@ -13077,10 +13081,10 @@
         <v>407</v>
       </c>
       <c r="L116">
-        <v>0.29399999999999998</v>
+        <v>6.6776370679380206E-2</v>
       </c>
       <c r="M116">
-        <v>0.11258428092517889</v>
+        <v>0.1125842809251789</v>
       </c>
       <c r="N116">
         <v>2</v>
@@ -13115,7 +13119,7 @@
         <v>407</v>
       </c>
       <c r="L117">
-        <v>0.65700000000000003</v>
+        <v>0.13848003562416505</v>
       </c>
       <c r="M117">
         <v>0.111804043038175</v>
@@ -13153,10 +13157,10 @@
         <v>407</v>
       </c>
       <c r="L118">
-        <v>9.375E-2</v>
+        <v>1.9609511106271776E-2</v>
       </c>
       <c r="M118">
-        <v>0.10987849581337431</v>
+        <v>0.10987849581337439</v>
       </c>
       <c r="N118">
         <v>4</v>
@@ -13191,7 +13195,7 @@
         <v>407</v>
       </c>
       <c r="L119">
-        <v>0.13275000000000001</v>
+        <v>2.9299333586547422E-2</v>
       </c>
       <c r="M119">
         <v>0</v>
@@ -13206,7 +13210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C038C1D4-726F-4EAD-893F-7DDE9AB84F19}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC829776-0CF7-4D84-91C6-D25659024241}">
   <dimension ref="B9:AB286"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13327,10 +13331,10 @@
         <v>960</v>
       </c>
       <c r="L11">
-        <v>1.08975</v>
+        <v>0.95117459245047398</v>
       </c>
       <c r="M11">
-        <v>0.61010244678045655</v>
+        <v>0.61010244471605635</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -13366,7 +13370,7 @@
         <v>3.3232499999999998</v>
       </c>
       <c r="AA11">
-        <v>0.4964752277914522</v>
+        <v>0.49647522779145237</v>
       </c>
       <c r="AB11">
         <v>2</v>
@@ -13401,10 +13405,10 @@
         <v>960</v>
       </c>
       <c r="L12">
-        <v>0.89700000000000002</v>
+        <v>0.69781583584602735</v>
       </c>
       <c r="M12">
-        <v>0.59396464564196261</v>
+        <v>0.59396464414765149</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -13475,10 +13479,10 @@
         <v>960</v>
       </c>
       <c r="L13">
-        <v>0.67800000000000005</v>
+        <v>0.50299000768639512</v>
       </c>
       <c r="M13">
-        <v>0.59112654371276352</v>
+        <v>0.59112654105297346</v>
       </c>
       <c r="N13">
         <v>2</v>
@@ -13549,10 +13553,10 @@
         <v>960</v>
       </c>
       <c r="L14">
-        <v>3.3000000000000002E-2</v>
+        <v>2.4359553319425693E-2</v>
       </c>
       <c r="M14">
-        <v>0.56926197987481464</v>
+        <v>0.56926197823113311</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -13623,10 +13627,10 @@
         <v>960</v>
       </c>
       <c r="L15">
-        <v>0.10425</v>
+        <v>7.6882109446146207E-2</v>
       </c>
       <c r="M15">
-        <v>0.55028984351397181</v>
+        <v>0.55028984187384211</v>
       </c>
       <c r="N15">
         <v>2</v>
@@ -13662,7 +13666,7 @@
         <v>8.3019999999999996</v>
       </c>
       <c r="AA15">
-        <v>0.48788193604133229</v>
+        <v>0.4878819360413324</v>
       </c>
       <c r="AB15">
         <v>4</v>
@@ -13697,10 +13701,10 @@
         <v>960</v>
       </c>
       <c r="L16">
-        <v>4.4999999999999997E-3</v>
+        <v>3.1010316875460576E-3</v>
       </c>
       <c r="M16">
-        <v>0.54951739215718887</v>
+        <v>0.54951739102042152</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -13771,10 +13775,10 @@
         <v>960</v>
       </c>
       <c r="L17">
-        <v>1.014</v>
+        <v>0.73116611927398445</v>
       </c>
       <c r="M17">
-        <v>0.54896921599633963</v>
+        <v>0.54896921313335556</v>
       </c>
       <c r="N17">
         <v>4</v>
@@ -13845,10 +13849,10 @@
         <v>960</v>
       </c>
       <c r="L18">
-        <v>1.6500000000000001E-2</v>
+        <v>1.1110172057116906E-2</v>
       </c>
       <c r="M18">
-        <v>0.54505029261507776</v>
+        <v>0.54505029062723043</v>
       </c>
       <c r="N18">
         <v>3</v>
@@ -13884,7 +13888,7 @@
         <v>9.4027499999999993</v>
       </c>
       <c r="AA18">
-        <v>0.48372514696005614</v>
+        <v>0.48372514696005636</v>
       </c>
       <c r="AB18">
         <v>5</v>
@@ -13919,10 +13923,10 @@
         <v>960</v>
       </c>
       <c r="L19">
-        <v>0.84450000000000003</v>
+        <v>0.73655880332368318</v>
       </c>
       <c r="M19">
-        <v>0.54277821993432507</v>
+        <v>0.54277821881364152</v>
       </c>
       <c r="N19">
         <v>2</v>
@@ -13993,10 +13997,10 @@
         <v>960</v>
       </c>
       <c r="L20">
-        <v>0.26324999999999998</v>
+        <v>0.19303194908716895</v>
       </c>
       <c r="M20">
-        <v>0.53744308167620503</v>
+        <v>0.53744307954031645</v>
       </c>
       <c r="N20">
         <v>1</v>
@@ -14067,10 +14071,10 @@
         <v>960</v>
       </c>
       <c r="L21">
-        <v>4.1250000000000002E-2</v>
+        <v>2.7169604316546768E-2</v>
       </c>
       <c r="M21">
-        <v>0.53129475560883488</v>
+        <v>0.53129475310244867</v>
       </c>
       <c r="N21">
         <v>5</v>
@@ -14106,7 +14110,7 @@
         <v>2.254</v>
       </c>
       <c r="AA21">
-        <v>0.4769655385811592</v>
+        <v>0.47696553858115931</v>
       </c>
       <c r="AB21">
         <v>2</v>
@@ -14141,10 +14145,10 @@
         <v>960</v>
       </c>
       <c r="L22">
-        <v>0.42525000000000002</v>
+        <v>0.30782598261617561</v>
       </c>
       <c r="M22">
-        <v>0.52820118005126515</v>
+        <v>0.52818009373295871</v>
       </c>
       <c r="N22">
         <v>1</v>
@@ -14215,10 +14219,10 @@
         <v>960</v>
       </c>
       <c r="L23">
-        <v>4.33575</v>
+        <v>2.6741887657279806</v>
       </c>
       <c r="M23">
-        <v>0.52779689732868262</v>
+        <v>0.5277969019041554</v>
       </c>
       <c r="N23">
         <v>2</v>
@@ -14289,10 +14293,10 @@
         <v>960</v>
       </c>
       <c r="L24">
-        <v>3.1259999999999999</v>
+        <v>1.8788113241354594</v>
       </c>
       <c r="M24">
-        <v>0.5277178809867803</v>
+        <v>0.52771787869925901</v>
       </c>
       <c r="N24">
         <v>3</v>
@@ -14363,10 +14367,10 @@
         <v>960</v>
       </c>
       <c r="L25">
-        <v>3.5804999999999998</v>
+        <v>2.171695910212716</v>
       </c>
       <c r="M25">
-        <v>0.52549117651119093</v>
+        <v>0.52549117175737969</v>
       </c>
       <c r="N25">
         <v>4</v>
@@ -14437,10 +14441,10 @@
         <v>960</v>
       </c>
       <c r="L26">
-        <v>1.1519999999999999</v>
+        <v>0.82332148286037199</v>
       </c>
       <c r="M26">
-        <v>0.52445107661641466</v>
+        <v>0.52447869138598835</v>
       </c>
       <c r="N26">
         <v>5</v>
@@ -14511,10 +14515,10 @@
         <v>960</v>
       </c>
       <c r="L27">
-        <v>9.39</v>
+        <v>5.6768603899734114</v>
       </c>
       <c r="M27">
-        <v>0.5217955840108186</v>
+        <v>0.52179633703589345</v>
       </c>
       <c r="N27">
         <v>3</v>
@@ -14550,7 +14554,7 @@
         <v>3.04325</v>
       </c>
       <c r="AA27">
-        <v>0.44868677715977262</v>
+        <v>0.44868677715977279</v>
       </c>
       <c r="AB27">
         <v>2</v>
@@ -14585,10 +14589,10 @@
         <v>960</v>
       </c>
       <c r="L28">
-        <v>4.0830000000000002</v>
+        <v>2.6141979104890614</v>
       </c>
       <c r="M28">
-        <v>0.52042123877936342</v>
+        <v>0.5204117762348115</v>
       </c>
       <c r="N28">
         <v>1</v>
@@ -14624,7 +14628,7 @@
         <v>13.223000000000001</v>
       </c>
       <c r="AA28">
-        <v>0.44637222892287198</v>
+        <v>0.44637222892287209</v>
       </c>
       <c r="AB28">
         <v>3</v>
@@ -14659,10 +14663,10 @@
         <v>960</v>
       </c>
       <c r="L29">
-        <v>5.3579999999999997</v>
+        <v>3.4168770969344311</v>
       </c>
       <c r="M29">
-        <v>0.517879042375466</v>
+        <v>0.51787952709957319</v>
       </c>
       <c r="N29">
         <v>2</v>
@@ -14733,10 +14737,10 @@
         <v>960</v>
       </c>
       <c r="L30">
-        <v>2.847</v>
+        <v>1.7093597264536589</v>
       </c>
       <c r="M30">
-        <v>0.5162315976661962</v>
+        <v>0.51623577971412404</v>
       </c>
       <c r="N30">
         <v>4</v>
@@ -14807,10 +14811,10 @@
         <v>960</v>
       </c>
       <c r="L31">
-        <v>20.569500000000001</v>
+        <v>12.907756600929234</v>
       </c>
       <c r="M31">
-        <v>0.50848571692923883</v>
+        <v>0.50850284508436339</v>
       </c>
       <c r="N31">
         <v>2</v>
@@ -14881,10 +14885,10 @@
         <v>960</v>
       </c>
       <c r="L32">
-        <v>10.58175</v>
+        <v>6.3528386832984296</v>
       </c>
       <c r="M32">
-        <v>0.50801987778797075</v>
+        <v>0.50799008132960444</v>
       </c>
       <c r="N32">
         <v>4</v>
@@ -14955,10 +14959,10 @@
         <v>960</v>
       </c>
       <c r="L33">
-        <v>6.5354999999999999</v>
+        <v>4.0567918098266986</v>
       </c>
       <c r="M33">
-        <v>0.50768991216098003</v>
+        <v>0.50784302950192672</v>
       </c>
       <c r="N33">
         <v>3</v>
@@ -15029,10 +15033,10 @@
         <v>960</v>
       </c>
       <c r="L34">
-        <v>16.085249999999998</v>
+        <v>10.38392489999214</v>
       </c>
       <c r="M34">
-        <v>0.50740651973019701</v>
+        <v>0.50739565571594447</v>
       </c>
       <c r="N34">
         <v>1</v>
@@ -15103,10 +15107,10 @@
         <v>960</v>
       </c>
       <c r="L35">
-        <v>1.6777500000000001</v>
+        <v>1.2076145955631625</v>
       </c>
       <c r="M35">
-        <v>0.50603377395520055</v>
+        <v>0.50603197934823463</v>
       </c>
       <c r="N35">
         <v>5</v>
@@ -15177,10 +15181,10 @@
         <v>960</v>
       </c>
       <c r="L36">
-        <v>30.155249999999999</v>
+        <v>19.258076410441795</v>
       </c>
       <c r="M36">
-        <v>0.502318975283782</v>
+        <v>0.5023016407962948</v>
       </c>
       <c r="N36">
         <v>1</v>
@@ -15251,10 +15255,10 @@
         <v>960</v>
       </c>
       <c r="L37">
-        <v>11.61825</v>
+        <v>6.8501167134225662</v>
       </c>
       <c r="M37">
-        <v>0.50108568239938167</v>
+        <v>0.50107796307281471</v>
       </c>
       <c r="N37">
         <v>4</v>
@@ -15290,7 +15294,7 @@
         <v>0.52675000000000005</v>
       </c>
       <c r="AA37">
-        <v>0.4002273545769226</v>
+        <v>0.40022735457692271</v>
       </c>
       <c r="AB37">
         <v>1</v>
@@ -15325,10 +15329,10 @@
         <v>960</v>
       </c>
       <c r="L38">
-        <v>17.202000000000002</v>
+        <v>10.635038576487077</v>
       </c>
       <c r="M38">
-        <v>0.50082736618069557</v>
+        <v>0.50080347796774749</v>
       </c>
       <c r="N38">
         <v>2</v>
@@ -15399,10 +15403,10 @@
         <v>960</v>
       </c>
       <c r="L39">
-        <v>20.293500000000002</v>
+        <v>12.205533851755641</v>
       </c>
       <c r="M39">
-        <v>0.49866971550511296</v>
+        <v>0.49866050147802232</v>
       </c>
       <c r="N39">
         <v>3</v>
@@ -15438,7 +15442,7 @@
         <v>3.8552499999999998</v>
       </c>
       <c r="AA39">
-        <v>0.39374077814246222</v>
+        <v>0.39374077814246228</v>
       </c>
       <c r="AB39">
         <v>1</v>
@@ -15473,10 +15477,10 @@
         <v>960</v>
       </c>
       <c r="L40">
-        <v>3.3022499999999999</v>
+        <v>2.3781795407348745</v>
       </c>
       <c r="M40">
-        <v>0.49684602050911214</v>
+        <v>0.49683561712335289</v>
       </c>
       <c r="N40">
         <v>5</v>
@@ -15547,10 +15551,10 @@
         <v>960</v>
       </c>
       <c r="L41">
-        <v>5.4675000000000002</v>
+        <v>3.2694431195334799</v>
       </c>
       <c r="M41">
-        <v>0.49240189605948703</v>
+        <v>0.49236457080148982</v>
       </c>
       <c r="N41">
         <v>3</v>
@@ -15586,7 +15590,7 @@
         <v>1.2004999999999999</v>
       </c>
       <c r="AA41">
-        <v>0.38004810242848031</v>
+        <v>0.38004810242848042</v>
       </c>
       <c r="AB41">
         <v>1</v>
@@ -15621,10 +15625,10 @@
         <v>960</v>
       </c>
       <c r="L42">
-        <v>7.2569999999999997</v>
+        <v>4.377905776516112</v>
       </c>
       <c r="M42">
-        <v>0.49132440529906468</v>
+        <v>0.49132863072620692</v>
       </c>
       <c r="N42">
         <v>4</v>
@@ -15660,7 +15664,7 @@
         <v>6.1249999999999999E-2</v>
       </c>
       <c r="AA42">
-        <v>0.3782849467552078</v>
+        <v>0.37828494675520791</v>
       </c>
       <c r="AB42">
         <v>2</v>
@@ -15695,10 +15699,10 @@
         <v>960</v>
       </c>
       <c r="L43">
-        <v>19.836749999999999</v>
+        <v>12.511890526193064</v>
       </c>
       <c r="M43">
-        <v>0.49093855041823392</v>
+        <v>0.49093562632299365</v>
       </c>
       <c r="N43">
         <v>2</v>
@@ -15734,7 +15738,7 @@
         <v>6.5957499999999998</v>
       </c>
       <c r="AA43">
-        <v>0.37163345868897291</v>
+        <v>0.37163345868897302</v>
       </c>
       <c r="AB43">
         <v>2</v>
@@ -15769,10 +15773,10 @@
         <v>960</v>
       </c>
       <c r="L44">
-        <v>20.62425</v>
+        <v>13.218610974251689</v>
       </c>
       <c r="M44">
-        <v>0.49010689652790823</v>
+        <v>0.49010396226497877</v>
       </c>
       <c r="N44">
         <v>1</v>
@@ -15843,10 +15847,10 @@
         <v>960</v>
       </c>
       <c r="L45">
-        <v>7.4152500000000003</v>
+        <v>4.3185693604022486</v>
       </c>
       <c r="M45">
-        <v>0.48926524345200995</v>
+        <v>0.48923996856856311</v>
       </c>
       <c r="N45">
         <v>5</v>
@@ -15917,10 +15921,10 @@
         <v>960</v>
       </c>
       <c r="L46">
-        <v>20.4315</v>
+        <v>11.770108926139839</v>
       </c>
       <c r="M46">
-        <v>0.48131492450288571</v>
+        <v>0.48129641604412554</v>
       </c>
       <c r="N46">
         <v>4</v>
@@ -15991,10 +15995,10 @@
         <v>960</v>
       </c>
       <c r="L47">
-        <v>22.363499999999998</v>
+        <v>13.295067652358656</v>
       </c>
       <c r="M47">
-        <v>0.48123358596105437</v>
+        <v>0.4812367299588074</v>
       </c>
       <c r="N47">
         <v>3</v>
@@ -16065,10 +16069,10 @@
         <v>960</v>
       </c>
       <c r="L48">
-        <v>20.846250000000001</v>
+        <v>13.257247953507003</v>
       </c>
       <c r="M48">
-        <v>0.48013816297123885</v>
+        <v>0.48014878222034629</v>
       </c>
       <c r="N48">
         <v>1</v>
@@ -16139,10 +16143,10 @@
         <v>960</v>
       </c>
       <c r="L49">
-        <v>21.713999999999999</v>
+        <v>13.24352046954415</v>
       </c>
       <c r="M49">
-        <v>0.47988527563536204</v>
+        <v>0.47999331585451599</v>
       </c>
       <c r="N49">
         <v>5</v>
@@ -16213,10 +16217,10 @@
         <v>960</v>
       </c>
       <c r="L50">
-        <v>18.892499999999998</v>
+        <v>11.719277007848788</v>
       </c>
       <c r="M50">
-        <v>0.47855125287937711</v>
+        <v>0.47852119530881687</v>
       </c>
       <c r="N50">
         <v>2</v>
@@ -16287,10 +16291,10 @@
         <v>960</v>
       </c>
       <c r="L51">
-        <v>38.427750000000003</v>
+        <v>23.895217296087846</v>
       </c>
       <c r="M51">
-        <v>0.47081466524176113</v>
+        <v>0.47081747055719286</v>
       </c>
       <c r="N51">
         <v>1</v>
@@ -16326,7 +16330,7 @@
         <v>3.5612499999999998</v>
       </c>
       <c r="AA51">
-        <v>0.34865419897566052</v>
+        <v>0.34865419897566063</v>
       </c>
       <c r="AB51">
         <v>1</v>
@@ -16361,10 +16365,10 @@
         <v>960</v>
       </c>
       <c r="L52">
-        <v>26.303249999999998</v>
+        <v>16.147757930119241</v>
       </c>
       <c r="M52">
-        <v>0.47061861894843532</v>
+        <v>0.4706023091757715</v>
       </c>
       <c r="N52">
         <v>2</v>
@@ -16400,7 +16404,7 @@
         <v>5.2744999999999997</v>
       </c>
       <c r="AA52">
-        <v>0.34781297393810279</v>
+        <v>0.3478129739381029</v>
       </c>
       <c r="AB52">
         <v>2</v>
@@ -16435,10 +16439,10 @@
         <v>960</v>
       </c>
       <c r="L53">
-        <v>34.881</v>
+        <v>20.678245433500894</v>
       </c>
       <c r="M53">
-        <v>0.46943481353849392</v>
+        <v>0.46941183389575908</v>
       </c>
       <c r="N53">
         <v>4</v>
@@ -16509,10 +16513,10 @@
         <v>960</v>
       </c>
       <c r="L54">
-        <v>33.029249999999998</v>
+        <v>19.645766461690442</v>
       </c>
       <c r="M54">
-        <v>0.4688581956670933</v>
+        <v>0.46887493450182199</v>
       </c>
       <c r="N54">
         <v>3</v>
@@ -16548,7 +16552,7 @@
         <v>8.0500000000000002E-2</v>
       </c>
       <c r="AA54">
-        <v>0.34458099924349678</v>
+        <v>0.34458099924349689</v>
       </c>
       <c r="AB54">
         <v>1</v>
@@ -16583,10 +16587,10 @@
         <v>960</v>
       </c>
       <c r="L55">
-        <v>26.34675</v>
+        <v>15.695746157239222</v>
       </c>
       <c r="M55">
-        <v>0.46857460076175655</v>
+        <v>0.46844079169872277</v>
       </c>
       <c r="N55">
         <v>5</v>
@@ -16657,10 +16661,10 @@
         <v>960</v>
       </c>
       <c r="L56">
-        <v>25.922999999999998</v>
+        <v>14.875817667724366</v>
       </c>
       <c r="M56">
-        <v>0.46193756107030298</v>
+        <v>0.4620060702740143</v>
       </c>
       <c r="N56">
         <v>5</v>
@@ -16731,10 +16735,10 @@
         <v>960</v>
       </c>
       <c r="L57">
-        <v>32.130749999999999</v>
+        <v>20.419597116043136</v>
       </c>
       <c r="M57">
-        <v>0.46081632865404887</v>
+        <v>0.4607848929533091</v>
       </c>
       <c r="N57">
         <v>1</v>
@@ -16770,7 +16774,7 @@
         <v>5.6420000000000003</v>
       </c>
       <c r="AA57">
-        <v>0.338089452401024</v>
+        <v>0.33808945240102412</v>
       </c>
       <c r="AB57">
         <v>3</v>
@@ -16805,10 +16809,10 @@
         <v>960</v>
       </c>
       <c r="L58">
-        <v>44.109000000000002</v>
+        <v>25.344573703009345</v>
       </c>
       <c r="M58">
-        <v>0.4600867319278204</v>
+        <v>0.46011390154008874</v>
       </c>
       <c r="N58">
         <v>4</v>
@@ -16879,10 +16883,10 @@
         <v>960</v>
       </c>
       <c r="L59">
-        <v>28.628250000000001</v>
+        <v>17.238042654730609</v>
       </c>
       <c r="M59">
-        <v>0.45935928924112862</v>
+        <v>0.45935598815717904</v>
       </c>
       <c r="N59">
         <v>3</v>
@@ -16953,10 +16957,10 @@
         <v>960</v>
       </c>
       <c r="L60">
-        <v>24.915749999999999</v>
+        <v>15.280440326505197</v>
       </c>
       <c r="M60">
-        <v>0.45843231813844509</v>
+        <v>0.45843325122864559</v>
       </c>
       <c r="N60">
         <v>2</v>
@@ -17027,10 +17031,10 @@
         <v>960</v>
       </c>
       <c r="L61">
-        <v>45.369750000000003</v>
+        <v>28.480222641568634</v>
       </c>
       <c r="M61">
-        <v>0.45049675508091985</v>
+        <v>0.45052751177397088</v>
       </c>
       <c r="N61">
         <v>1</v>
@@ -17101,10 +17105,10 @@
         <v>960</v>
       </c>
       <c r="L62">
-        <v>43.014749999999999</v>
+        <v>26.40644429118505</v>
       </c>
       <c r="M62">
-        <v>0.45033616290957135</v>
+        <v>0.45034516106530764</v>
       </c>
       <c r="N62">
         <v>2</v>
@@ -17175,10 +17179,10 @@
         <v>960</v>
       </c>
       <c r="L63">
-        <v>46.031999999999996</v>
+        <v>26.059783037631473</v>
       </c>
       <c r="M63">
-        <v>0.44980160137162478</v>
+        <v>0.44987566721244177</v>
       </c>
       <c r="N63">
         <v>5</v>
@@ -17249,10 +17253,10 @@
         <v>960</v>
       </c>
       <c r="L64">
-        <v>63.573</v>
+        <v>36.666162109399643</v>
       </c>
       <c r="M64">
-        <v>0.44961397179935897</v>
+        <v>0.44957309958979286</v>
       </c>
       <c r="N64">
         <v>4</v>
@@ -17323,10 +17327,10 @@
         <v>960</v>
       </c>
       <c r="L65">
-        <v>38.670749999999998</v>
+        <v>22.997165211618693</v>
       </c>
       <c r="M65">
-        <v>0.44934577643945783</v>
+        <v>0.44935175976355513</v>
       </c>
       <c r="N65">
         <v>3</v>
@@ -17362,7 +17366,7 @@
         <v>0.59499999999999997</v>
       </c>
       <c r="AA65">
-        <v>0.28585799300814968</v>
+        <v>0.28585799300814979</v>
       </c>
       <c r="AB65">
         <v>1</v>
@@ -17397,10 +17401,10 @@
         <v>960</v>
       </c>
       <c r="L66">
-        <v>38.439</v>
+        <v>23.409626303578243</v>
       </c>
       <c r="M66">
-        <v>0.4403747063989889</v>
+        <v>0.44037058720822553</v>
       </c>
       <c r="N66">
         <v>3</v>
@@ -17436,7 +17440,7 @@
         <v>2.2487499999999998</v>
       </c>
       <c r="AA66">
-        <v>0.28359206425078048</v>
+        <v>0.2835920642507806</v>
       </c>
       <c r="AB66">
         <v>1</v>
@@ -17471,10 +17475,10 @@
         <v>960</v>
       </c>
       <c r="L67">
-        <v>33.713999999999999</v>
+        <v>21.423089555495963</v>
       </c>
       <c r="M67">
-        <v>0.43936584635600928</v>
+        <v>0.4393796077606843</v>
       </c>
       <c r="N67">
         <v>1</v>
@@ -17545,10 +17549,10 @@
         <v>960</v>
       </c>
       <c r="L68">
-        <v>32.764499999999998</v>
+        <v>20.193043929524354</v>
       </c>
       <c r="M68">
-        <v>0.43870587166770925</v>
+        <v>0.43872553476658549</v>
       </c>
       <c r="N68">
         <v>2</v>
@@ -17584,7 +17588,7 @@
         <v>3.3250000000000002E-2</v>
       </c>
       <c r="AA68">
-        <v>0.27045126434738781</v>
+        <v>0.27045126434738792</v>
       </c>
       <c r="AB68">
         <v>2</v>
@@ -17619,10 +17623,10 @@
         <v>960</v>
       </c>
       <c r="L69">
-        <v>22.928999999999998</v>
+        <v>13.299451603998955</v>
       </c>
       <c r="M69">
-        <v>0.43845249858864788</v>
+        <v>0.43850385877202663</v>
       </c>
       <c r="N69">
         <v>4</v>
@@ -17693,10 +17697,10 @@
         <v>960</v>
       </c>
       <c r="L70">
-        <v>32.723999999999997</v>
+        <v>18.3484841368203</v>
       </c>
       <c r="M70">
-        <v>0.43787512186375221</v>
+        <v>0.43791945248539965</v>
       </c>
       <c r="N70">
         <v>5</v>
@@ -17767,10 +17771,10 @@
         <v>960</v>
       </c>
       <c r="L71">
-        <v>40.521000000000001</v>
+        <v>25.162835560405298</v>
       </c>
       <c r="M71">
-        <v>0.43045401339884964</v>
+        <v>0.43045540192701359</v>
       </c>
       <c r="N71">
         <v>2</v>
@@ -17841,10 +17845,10 @@
         <v>960</v>
       </c>
       <c r="L72">
-        <v>48.684750000000001</v>
+        <v>29.91201835811443</v>
       </c>
       <c r="M72">
-        <v>0.42982361749876685</v>
+        <v>0.42982771935849978</v>
       </c>
       <c r="N72">
         <v>3</v>
@@ -17915,10 +17919,10 @@
         <v>960</v>
       </c>
       <c r="L73">
-        <v>55.921500000000002</v>
+        <v>31.038275692876297</v>
       </c>
       <c r="M73">
-        <v>0.42957089173962087</v>
+        <v>0.42960306367419843</v>
       </c>
       <c r="N73">
         <v>5</v>
@@ -17989,10 +17993,10 @@
         <v>960</v>
       </c>
       <c r="L74">
-        <v>43.938749999999999</v>
+        <v>27.795143392808402</v>
       </c>
       <c r="M74">
-        <v>0.42909823539578695</v>
+        <v>0.4290937163005562</v>
       </c>
       <c r="N74">
         <v>1</v>
@@ -18063,10 +18067,10 @@
         <v>960</v>
       </c>
       <c r="L75">
-        <v>42.273000000000003</v>
+        <v>25.266725639925053</v>
       </c>
       <c r="M75">
-        <v>0.42894368481941414</v>
+        <v>0.42889320082961324</v>
       </c>
       <c r="N75">
         <v>4</v>
@@ -18102,7 +18106,7 @@
         <v>5.9972500000000002</v>
       </c>
       <c r="AA75">
-        <v>0.25454463398137389</v>
+        <v>0.254544633981374</v>
       </c>
       <c r="AB75">
         <v>5</v>
@@ -18137,10 +18141,10 @@
         <v>960</v>
       </c>
       <c r="L76">
-        <v>33.887250000000002</v>
+        <v>20.813346733618015</v>
       </c>
       <c r="M76">
-        <v>0.42359935639506863</v>
+        <v>0.42359224600722245</v>
       </c>
       <c r="N76">
         <v>3</v>
@@ -18211,10 +18215,10 @@
         <v>960</v>
       </c>
       <c r="L77">
-        <v>48.75</v>
+        <v>30.094823504938621</v>
       </c>
       <c r="M77">
-        <v>0.42052848592766812</v>
+        <v>0.4205585847710761</v>
       </c>
       <c r="N77">
         <v>2</v>
@@ -18250,7 +18254,7 @@
         <v>3.81325</v>
       </c>
       <c r="AA77">
-        <v>0.25333024014030647</v>
+        <v>0.25333024014030658</v>
       </c>
       <c r="AB77">
         <v>2</v>
@@ -18285,10 +18289,10 @@
         <v>960</v>
       </c>
       <c r="L78">
-        <v>37.119</v>
+        <v>21.046306243125958</v>
       </c>
       <c r="M78">
-        <v>0.41983990353348144</v>
+        <v>0.41983127582810953</v>
       </c>
       <c r="N78">
         <v>5</v>
@@ -18359,10 +18363,10 @@
         <v>960</v>
       </c>
       <c r="L79">
-        <v>46.176749999999998</v>
+        <v>29.42795933254947</v>
       </c>
       <c r="M79">
-        <v>0.41958633520081257</v>
+        <v>0.41959509180366156</v>
       </c>
       <c r="N79">
         <v>1</v>
@@ -18433,10 +18437,10 @@
         <v>960</v>
       </c>
       <c r="L80">
-        <v>40.353749999999998</v>
+        <v>23.664797745589972</v>
       </c>
       <c r="M80">
-        <v>0.41947685977643928</v>
+        <v>0.41945571983782298</v>
       </c>
       <c r="N80">
         <v>4</v>
@@ -18472,7 +18476,7 @@
         <v>2.4815</v>
       </c>
       <c r="AA80">
-        <v>0.2447912658328355</v>
+        <v>0.24479126583283559</v>
       </c>
       <c r="AB80">
         <v>4</v>
@@ -18507,10 +18511,10 @@
         <v>960</v>
       </c>
       <c r="L81">
-        <v>18.391500000000001</v>
+        <v>11.499363984235744</v>
       </c>
       <c r="M81">
-        <v>0.41220404504979652</v>
+        <v>0.41220804179158416</v>
       </c>
       <c r="N81">
         <v>2</v>
@@ -18581,10 +18585,10 @@
         <v>960</v>
       </c>
       <c r="L82">
-        <v>28.627500000000001</v>
+        <v>16.175621264054392</v>
       </c>
       <c r="M82">
-        <v>0.40988982438334826</v>
+        <v>0.4099120712215833</v>
       </c>
       <c r="N82">
         <v>4</v>
@@ -18655,10 +18659,10 @@
         <v>960</v>
       </c>
       <c r="L83">
-        <v>31.539000000000001</v>
+        <v>19.89980399258258</v>
       </c>
       <c r="M83">
-        <v>0.40964065775305386</v>
+        <v>0.40964105007762991</v>
       </c>
       <c r="N83">
         <v>1</v>
@@ -18729,10 +18733,10 @@
         <v>960</v>
       </c>
       <c r="L84">
-        <v>25.243500000000001</v>
+        <v>15.073091467522854</v>
       </c>
       <c r="M84">
-        <v>0.40946124166546743</v>
+        <v>0.40946203727135611</v>
       </c>
       <c r="N84">
         <v>3</v>
@@ -18803,10 +18807,10 @@
         <v>960</v>
       </c>
       <c r="L85">
-        <v>25.635000000000002</v>
+        <v>14.814557986863617</v>
       </c>
       <c r="M85">
-        <v>0.40826684448370471</v>
+        <v>0.40834190958956823</v>
       </c>
       <c r="N85">
         <v>5</v>
@@ -18877,10 +18881,10 @@
         <v>960</v>
       </c>
       <c r="L86">
-        <v>28.797750000000001</v>
+        <v>18.087912925065094</v>
       </c>
       <c r="M86">
-        <v>0.40156839300798192</v>
+        <v>0.40157594131588892</v>
       </c>
       <c r="N86">
         <v>1</v>
@@ -18951,10 +18955,10 @@
         <v>960</v>
       </c>
       <c r="L87">
-        <v>25.524750000000001</v>
+        <v>14.390989130962943</v>
       </c>
       <c r="M87">
-        <v>0.39888461047308188</v>
+        <v>0.39871874892260811</v>
       </c>
       <c r="N87">
         <v>5</v>
@@ -18990,7 +18994,7 @@
         <v>8.9547500000000007</v>
       </c>
       <c r="AA87">
-        <v>0.22705102286584891</v>
+        <v>0.22705102286584897</v>
       </c>
       <c r="AB87">
         <v>4</v>
@@ -19025,10 +19029,10 @@
         <v>960</v>
       </c>
       <c r="L88">
-        <v>28.21875</v>
+        <v>17.722040787519067</v>
       </c>
       <c r="M88">
-        <v>0.39872486177413569</v>
+        <v>0.39868780582598334</v>
       </c>
       <c r="N88">
         <v>2</v>
@@ -19099,10 +19103,10 @@
         <v>960</v>
       </c>
       <c r="L89">
-        <v>33.398249999999997</v>
+        <v>19.951369582186711</v>
       </c>
       <c r="M89">
-        <v>0.39824260939475831</v>
+        <v>0.39823320780126792</v>
       </c>
       <c r="N89">
         <v>3</v>
@@ -19173,10 +19177,10 @@
         <v>960</v>
       </c>
       <c r="L90">
-        <v>30.795000000000002</v>
+        <v>18.047822621975069</v>
       </c>
       <c r="M90">
-        <v>0.39810954924148373</v>
+        <v>0.39815018822872511</v>
       </c>
       <c r="N90">
         <v>4</v>
@@ -19247,10 +19251,10 @@
         <v>960</v>
       </c>
       <c r="L91">
-        <v>38.084249999999997</v>
+        <v>21.051785484010168</v>
       </c>
       <c r="M91">
-        <v>0.39187233418715123</v>
+        <v>0.39189988324629688</v>
       </c>
       <c r="N91">
         <v>4</v>
@@ -19286,7 +19290,7 @@
         <v>0.80674999999999997</v>
       </c>
       <c r="AA91">
-        <v>0.2233227860037999</v>
+        <v>0.22332278600380001</v>
       </c>
       <c r="AB91">
         <v>4</v>
@@ -19321,10 +19325,10 @@
         <v>960</v>
       </c>
       <c r="L92">
-        <v>21.068999999999999</v>
+        <v>11.72903533193306</v>
       </c>
       <c r="M92">
-        <v>0.39150202951675911</v>
+        <v>0.39159457920431234</v>
       </c>
       <c r="N92">
         <v>5</v>
@@ -19360,7 +19364,7 @@
         <v>6.2597500000000004</v>
       </c>
       <c r="AA92">
-        <v>0.2231349194602136</v>
+        <v>0.22313491946021372</v>
       </c>
       <c r="AB92">
         <v>5</v>
@@ -19395,10 +19399,10 @@
         <v>960</v>
       </c>
       <c r="L93">
-        <v>20.844000000000001</v>
+        <v>13.106152040918372</v>
       </c>
       <c r="M93">
-        <v>0.39011087253649834</v>
+        <v>0.39013350396355873</v>
       </c>
       <c r="N93">
         <v>1</v>
@@ -19434,7 +19438,7 @@
         <v>2.4359999999999999</v>
       </c>
       <c r="AA93">
-        <v>0.22190343288963196</v>
+        <v>0.22190343288963207</v>
       </c>
       <c r="AB93">
         <v>2</v>
@@ -19469,10 +19473,10 @@
         <v>960</v>
       </c>
       <c r="L94">
-        <v>17.166</v>
+        <v>10.505545227627413</v>
       </c>
       <c r="M94">
-        <v>0.39001973751125618</v>
+        <v>0.39000503744446774</v>
       </c>
       <c r="N94">
         <v>2</v>
@@ -19508,7 +19512,7 @@
         <v>3.77475</v>
       </c>
       <c r="AA94">
-        <v>0.2216249815925859</v>
+        <v>0.22162498159258601</v>
       </c>
       <c r="AB94">
         <v>3</v>
@@ -19543,10 +19547,10 @@
         <v>960</v>
       </c>
       <c r="L95">
-        <v>28.152000000000001</v>
+        <v>16.295487393838535</v>
       </c>
       <c r="M95">
-        <v>0.38947745643731807</v>
+        <v>0.38952720544968089</v>
       </c>
       <c r="N95">
         <v>3</v>
@@ -19617,10 +19621,10 @@
         <v>960</v>
       </c>
       <c r="L96">
-        <v>25.4055</v>
+        <v>15.924581528802701</v>
       </c>
       <c r="M96">
-        <v>0.38077048280981662</v>
+        <v>0.38075286518785467</v>
       </c>
       <c r="N96">
         <v>1</v>
@@ -19691,10 +19695,10 @@
         <v>960</v>
       </c>
       <c r="L97">
-        <v>21.338999999999999</v>
+        <v>10.83965993333099</v>
       </c>
       <c r="M97">
-        <v>0.38071715014964813</v>
+        <v>0.38068434847310412</v>
       </c>
       <c r="N97">
         <v>5</v>
@@ -19730,7 +19734,7 @@
         <v>1.2617499999999999</v>
       </c>
       <c r="AA97">
-        <v>0.21038310072991737</v>
+        <v>0.2103831007299175</v>
       </c>
       <c r="AB97">
         <v>3</v>
@@ -19765,10 +19769,10 @@
         <v>960</v>
       </c>
       <c r="L98">
-        <v>27.957750000000001</v>
+        <v>15.333661243456108</v>
       </c>
       <c r="M98">
-        <v>0.38033296202631739</v>
+        <v>0.38030571989551554</v>
       </c>
       <c r="N98">
         <v>4</v>
@@ -19839,10 +19843,10 @@
         <v>960</v>
       </c>
       <c r="L99">
-        <v>20.759250000000002</v>
+        <v>12.531619319830972</v>
       </c>
       <c r="M99">
-        <v>0.38017969426042164</v>
+        <v>0.38022099767275663</v>
       </c>
       <c r="N99">
         <v>2</v>
@@ -19878,7 +19882,7 @@
         <v>6.6185</v>
       </c>
       <c r="AA99">
-        <v>0.20908396945805774</v>
+        <v>0.20908396945805779</v>
       </c>
       <c r="AB99">
         <v>1</v>
@@ -19913,10 +19917,10 @@
         <v>960</v>
       </c>
       <c r="L100">
-        <v>48.033749999999998</v>
+        <v>28.307674344167761</v>
       </c>
       <c r="M100">
-        <v>0.37985194853582349</v>
+        <v>0.37979913030795781</v>
       </c>
       <c r="N100">
         <v>3</v>
@@ -19987,10 +19991,10 @@
         <v>960</v>
       </c>
       <c r="L101">
-        <v>22.361999999999998</v>
+        <v>13.08783495595233</v>
       </c>
       <c r="M101">
-        <v>0.3702532214902754</v>
+        <v>0.37029776655807711</v>
       </c>
       <c r="N101">
         <v>3</v>
@@ -20026,7 +20030,7 @@
         <v>3.2392500000000002</v>
       </c>
       <c r="AA101">
-        <v>0.1995699016482943</v>
+        <v>0.19956990164829433</v>
       </c>
       <c r="AB101">
         <v>4</v>
@@ -20061,10 +20065,10 @@
         <v>960</v>
       </c>
       <c r="L102">
-        <v>26.616</v>
+        <v>15.2426099224244</v>
       </c>
       <c r="M102">
-        <v>0.37000744384600665</v>
+        <v>0.36999105775522539</v>
       </c>
       <c r="N102">
         <v>4</v>
@@ -20135,10 +20139,10 @@
         <v>960</v>
       </c>
       <c r="L103">
-        <v>22.1355</v>
+        <v>13.761644566092331</v>
       </c>
       <c r="M103">
-        <v>0.36885413517853888</v>
+        <v>0.36886301249164632</v>
       </c>
       <c r="N103">
         <v>1</v>
@@ -20209,10 +20213,10 @@
         <v>960</v>
       </c>
       <c r="L104">
-        <v>10.0425</v>
+        <v>6.4032658903069324</v>
       </c>
       <c r="M104">
-        <v>0.36864586596202448</v>
+        <v>0.36866919832816436</v>
       </c>
       <c r="N104">
         <v>2</v>
@@ -20283,10 +20287,10 @@
         <v>960</v>
       </c>
       <c r="L105">
-        <v>22.02225</v>
+        <v>11.117280993151141</v>
       </c>
       <c r="M105">
-        <v>0.36790790739406509</v>
+        <v>0.36793401625286315</v>
       </c>
       <c r="N105">
         <v>5</v>
@@ -20357,10 +20361,10 @@
         <v>960</v>
       </c>
       <c r="L106">
-        <v>11.601749999999999</v>
+        <v>7.2638648089109914</v>
       </c>
       <c r="M106">
-        <v>0.36093934122778754</v>
+        <v>0.36092339371107579</v>
       </c>
       <c r="N106">
         <v>1</v>
@@ -20396,7 +20400,7 @@
         <v>0.46200000000000002</v>
       </c>
       <c r="AA106">
-        <v>0.1908987430933507</v>
+        <v>0.19089874309335081</v>
       </c>
       <c r="AB106">
         <v>3</v>
@@ -20431,10 +20435,10 @@
         <v>960</v>
       </c>
       <c r="L107">
-        <v>24.356999999999999</v>
+        <v>14.619799302359967</v>
       </c>
       <c r="M107">
-        <v>0.36046141923824288</v>
+        <v>0.36033593452746271</v>
       </c>
       <c r="N107">
         <v>3</v>
@@ -20505,10 +20509,10 @@
         <v>960</v>
       </c>
       <c r="L108">
-        <v>5.7149999999999999</v>
+        <v>3.4455245223053126</v>
       </c>
       <c r="M108">
-        <v>0.35962743572134853</v>
+        <v>0.35961313205516421</v>
       </c>
       <c r="N108">
         <v>2</v>
@@ -20579,10 +20583,10 @@
         <v>960</v>
       </c>
       <c r="L109">
-        <v>22.917750000000002</v>
+        <v>11.985343912728748</v>
       </c>
       <c r="M109">
-        <v>0.35956051806128153</v>
+        <v>0.35930876397578326</v>
       </c>
       <c r="N109">
         <v>5</v>
@@ -20618,7 +20622,7 @@
         <v>2.0405000000000002</v>
       </c>
       <c r="AA109">
-        <v>0.1864780609731318</v>
+        <v>0.18647806097313191</v>
       </c>
       <c r="AB109">
         <v>4</v>
@@ -20653,10 +20657,10 @@
         <v>960</v>
       </c>
       <c r="L110">
-        <v>30.135000000000002</v>
+        <v>17.012223290364449</v>
       </c>
       <c r="M110">
-        <v>0.35923119834292661</v>
+        <v>0.35920163451009007</v>
       </c>
       <c r="N110">
         <v>4</v>
@@ -20727,10 +20731,10 @@
         <v>960</v>
       </c>
       <c r="L111">
-        <v>13.03725</v>
+        <v>7.7452249824568762</v>
       </c>
       <c r="M111">
-        <v>0.35104835542176555</v>
+        <v>0.35105668062220385</v>
       </c>
       <c r="N111">
         <v>3</v>
@@ -20801,10 +20805,10 @@
         <v>960</v>
       </c>
       <c r="L112">
-        <v>28.356000000000002</v>
+        <v>15.691056457875591</v>
       </c>
       <c r="M112">
-        <v>0.35039406981610632</v>
+        <v>0.35039357052132369</v>
       </c>
       <c r="N112">
         <v>5</v>
@@ -20840,7 +20844,7 @@
         <v>0.50224999999999997</v>
       </c>
       <c r="AA112">
-        <v>0.18066635341722512</v>
+        <v>0.18066635341722515</v>
       </c>
       <c r="AB112">
         <v>2</v>
@@ -20875,10 +20879,10 @@
         <v>960</v>
       </c>
       <c r="L113">
-        <v>22.825500000000002</v>
+        <v>13.746296190742294</v>
       </c>
       <c r="M113">
-        <v>0.34925380581894283</v>
+        <v>0.34934528456330649</v>
       </c>
       <c r="N113">
         <v>4</v>
@@ -20949,10 +20953,10 @@
         <v>960</v>
       </c>
       <c r="L114">
-        <v>12.531750000000001</v>
+        <v>7.5319959814796702</v>
       </c>
       <c r="M114">
-        <v>0.34915095272832208</v>
+        <v>0.34910805193663724</v>
       </c>
       <c r="N114">
         <v>2</v>
@@ -21023,10 +21027,10 @@
         <v>960</v>
       </c>
       <c r="L115">
-        <v>28.727250000000002</v>
+        <v>18.337302652561895</v>
       </c>
       <c r="M115">
-        <v>0.34798342409344057</v>
+        <v>0.34796318750716798</v>
       </c>
       <c r="N115">
         <v>1</v>
@@ -21097,10 +21101,10 @@
         <v>960</v>
       </c>
       <c r="L116">
-        <v>23.577000000000002</v>
+        <v>13.707395276024013</v>
       </c>
       <c r="M116">
-        <v>0.34074230936876648</v>
+        <v>0.34053417923550777</v>
       </c>
       <c r="N116">
         <v>4</v>
@@ -21171,10 +21175,10 @@
         <v>960</v>
       </c>
       <c r="L117">
-        <v>28.03425</v>
+        <v>17.417216622364652</v>
       </c>
       <c r="M117">
-        <v>0.33978219730855125</v>
+        <v>0.33977701554736406</v>
       </c>
       <c r="N117">
         <v>1</v>
@@ -21245,10 +21249,10 @@
         <v>960</v>
       </c>
       <c r="L118">
-        <v>27.138000000000002</v>
+        <v>15.966842300630992</v>
       </c>
       <c r="M118">
-        <v>0.33959891662573555</v>
+        <v>0.33964748006169387</v>
       </c>
       <c r="N118">
         <v>3</v>
@@ -21284,7 +21288,7 @@
         <v>3.4667500000000002</v>
       </c>
       <c r="AA118">
-        <v>0.1680573115967598</v>
+        <v>0.16805731159675991</v>
       </c>
       <c r="AB118">
         <v>4</v>
@@ -21319,10 +21323,10 @@
         <v>960</v>
       </c>
       <c r="L119">
-        <v>27.049499999999998</v>
+        <v>13.543157740642444</v>
       </c>
       <c r="M119">
-        <v>0.33948867931176085</v>
+        <v>0.33957701495422093</v>
       </c>
       <c r="N119">
         <v>5</v>
@@ -21358,7 +21362,7 @@
         <v>0.86099999999999999</v>
       </c>
       <c r="AA119">
-        <v>0.16567717080433567</v>
+        <v>0.16567717080433575</v>
       </c>
       <c r="AB119">
         <v>5</v>
@@ -21393,10 +21397,10 @@
         <v>960</v>
       </c>
       <c r="L120">
-        <v>19.949249999999999</v>
+        <v>11.789468034903519</v>
       </c>
       <c r="M120">
-        <v>0.33878925105715424</v>
+        <v>0.33880891724386947</v>
       </c>
       <c r="N120">
         <v>2</v>
@@ -21467,10 +21471,10 @@
         <v>960</v>
       </c>
       <c r="L121">
-        <v>21.771750000000001</v>
+        <v>12.010656707060956</v>
       </c>
       <c r="M121">
-        <v>0.33084644201591273</v>
+        <v>0.33073577405354815</v>
       </c>
       <c r="N121">
         <v>4</v>
@@ -21506,7 +21510,7 @@
         <v>2.4482499999999998</v>
       </c>
       <c r="AA121">
-        <v>0.16131698968088995</v>
+        <v>0.16131698968089006</v>
       </c>
       <c r="AB121">
         <v>1</v>
@@ -21541,10 +21545,10 @@
         <v>960</v>
       </c>
       <c r="L122">
-        <v>31.095749999999999</v>
+        <v>18.753985217042196</v>
       </c>
       <c r="M122">
-        <v>0.3294855784524765</v>
+        <v>0.32963427903011383</v>
       </c>
       <c r="N122">
         <v>2</v>
@@ -21615,10 +21619,10 @@
         <v>960</v>
       </c>
       <c r="L123">
-        <v>12.69675</v>
+        <v>7.4161649660043301</v>
       </c>
       <c r="M123">
-        <v>0.3290635783093338</v>
+        <v>0.32902734124100141</v>
       </c>
       <c r="N123">
         <v>3</v>
@@ -21654,7 +21658,7 @@
         <v>0.93625000000000003</v>
       </c>
       <c r="AA123">
-        <v>0.15883447213246996</v>
+        <v>0.15883447213247001</v>
       </c>
       <c r="AB123">
         <v>2</v>
@@ -21689,10 +21693,10 @@
         <v>960</v>
       </c>
       <c r="L124">
-        <v>34.075499999999998</v>
+        <v>21.172298662005705</v>
       </c>
       <c r="M124">
-        <v>0.32891539956833105</v>
+        <v>0.32890748728687524</v>
       </c>
       <c r="N124">
         <v>1</v>
@@ -21763,10 +21767,10 @@
         <v>960</v>
       </c>
       <c r="L125">
-        <v>23.412749999999999</v>
+        <v>11.856172117758316</v>
       </c>
       <c r="M125">
-        <v>0.32832778764926129</v>
+        <v>0.32835539934091507</v>
       </c>
       <c r="N125">
         <v>5</v>
@@ -21837,10 +21841,10 @@
         <v>960</v>
       </c>
       <c r="L126">
-        <v>16.480499999999999</v>
+        <v>8.6484581923032131</v>
       </c>
       <c r="M126">
-        <v>0.3207600790776477</v>
+        <v>0.32074754340602513</v>
       </c>
       <c r="N126">
         <v>5</v>
@@ -21911,10 +21915,10 @@
         <v>960</v>
       </c>
       <c r="L127">
-        <v>41.608499999999999</v>
+        <v>25.592904599585829</v>
       </c>
       <c r="M127">
-        <v>0.32052588721586411</v>
+        <v>0.32049875048451942</v>
       </c>
       <c r="N127">
         <v>1</v>
@@ -21950,7 +21954,7 @@
         <v>0.46550000000000002</v>
       </c>
       <c r="AA127">
-        <v>0.15005816748017262</v>
+        <v>0.15005816748017267</v>
       </c>
       <c r="AB127">
         <v>1</v>
@@ -21985,10 +21989,10 @@
         <v>960</v>
       </c>
       <c r="L128">
-        <v>26.199750000000002</v>
+        <v>15.106119584542132</v>
       </c>
       <c r="M128">
-        <v>0.32019272886493028</v>
+        <v>0.32017598714988293</v>
       </c>
       <c r="N128">
         <v>3</v>
@@ -22024,7 +22028,7 @@
         <v>8.5820000000000007</v>
       </c>
       <c r="AA128">
-        <v>0.1480787400740359</v>
+        <v>0.14807874007403596</v>
       </c>
       <c r="AB128">
         <v>5</v>
@@ -22059,10 +22063,10 @@
         <v>960</v>
       </c>
       <c r="L129">
-        <v>16.555499999999999</v>
+        <v>9.9263648155653144</v>
       </c>
       <c r="M129">
-        <v>0.32000951690630397</v>
+        <v>0.31999054375813041</v>
       </c>
       <c r="N129">
         <v>2</v>
@@ -22133,10 +22137,10 @@
         <v>960</v>
       </c>
       <c r="L130">
-        <v>18.1905</v>
+        <v>10.109382667375774</v>
       </c>
       <c r="M130">
-        <v>0.31978691526076847</v>
+        <v>0.31978242404294493</v>
       </c>
       <c r="N130">
         <v>4</v>
@@ -22207,13 +22211,13 @@
         <v>960</v>
       </c>
       <c r="L131">
-        <v>27.611999999999998</v>
+        <v>21.531235379188558</v>
       </c>
       <c r="M131">
-        <v>0.31131469730384698</v>
+        <v>0.31129158813214458</v>
       </c>
       <c r="N131">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P131" t="s">
         <v>182</v>
@@ -22281,13 +22285,13 @@
         <v>960</v>
       </c>
       <c r="L132">
-        <v>34.508249999999997</v>
+        <v>15.659922732362032</v>
       </c>
       <c r="M132">
-        <v>0.31130549433183557</v>
+        <v>0.31128876929451893</v>
       </c>
       <c r="N132">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P132" t="s">
         <v>182</v>
@@ -22355,10 +22359,10 @@
         <v>960</v>
       </c>
       <c r="L133">
-        <v>21.885750000000002</v>
+        <v>12.838018809925224</v>
       </c>
       <c r="M133">
-        <v>0.31115945773911358</v>
+        <v>0.31114197616693484</v>
       </c>
       <c r="N133">
         <v>2</v>
@@ -22394,7 +22398,7 @@
         <v>6.3542500000000004</v>
       </c>
       <c r="AA133">
-        <v>0.13842545494088382</v>
+        <v>0.1384254549408839</v>
       </c>
       <c r="AB133">
         <v>2</v>
@@ -22429,10 +22433,10 @@
         <v>960</v>
       </c>
       <c r="L134">
-        <v>33.125999999999998</v>
+        <v>14.797164236649779</v>
       </c>
       <c r="M134">
-        <v>0.31012800664746837</v>
+        <v>0.31005811466401373</v>
       </c>
       <c r="N134">
         <v>5</v>
@@ -22468,7 +22472,7 @@
         <v>1.5907500000000001</v>
       </c>
       <c r="AA134">
-        <v>0.13731043428898798</v>
+        <v>0.13731043428898806</v>
       </c>
       <c r="AB134">
         <v>5</v>
@@ -22503,10 +22507,10 @@
         <v>960</v>
       </c>
       <c r="L135">
-        <v>27.442499999999999</v>
+        <v>15.478844336998025</v>
       </c>
       <c r="M135">
-        <v>0.30982181903410416</v>
+        <v>0.30981064986963319</v>
       </c>
       <c r="N135">
         <v>4</v>
@@ -22542,7 +22546,7 @@
         <v>2.3029999999999999</v>
       </c>
       <c r="AA135">
-        <v>0.13476498094377387</v>
+        <v>0.13476498094377395</v>
       </c>
       <c r="AB135">
         <v>1</v>
@@ -22577,10 +22581,10 @@
         <v>960</v>
       </c>
       <c r="L136">
-        <v>18.7425</v>
+        <v>10.277298653933357</v>
       </c>
       <c r="M136">
-        <v>0.30138452704845509</v>
+        <v>0.301350562014495</v>
       </c>
       <c r="N136">
         <v>3</v>
@@ -22616,7 +22620,7 @@
         <v>0.66500000000000004</v>
       </c>
       <c r="AA136">
-        <v>0.13460568295982811</v>
+        <v>0.13460568295982819</v>
       </c>
       <c r="AB136">
         <v>5</v>
@@ -22651,10 +22655,10 @@
         <v>960</v>
       </c>
       <c r="L137">
-        <v>35.582250000000002</v>
+        <v>21.842668600164536</v>
       </c>
       <c r="M137">
-        <v>0.3002480074027476</v>
+        <v>0.30026601601235353</v>
       </c>
       <c r="N137">
         <v>1</v>
@@ -22725,10 +22729,10 @@
         <v>960</v>
       </c>
       <c r="L138">
-        <v>24.45</v>
+        <v>14.913061220014834</v>
       </c>
       <c r="M138">
-        <v>0.2998325866618225</v>
+        <v>0.29963342296095002</v>
       </c>
       <c r="N138">
         <v>2</v>
@@ -22799,10 +22803,10 @@
         <v>960</v>
       </c>
       <c r="L139">
-        <v>16.080749999999998</v>
+        <v>7.6684411576885587</v>
       </c>
       <c r="M139">
-        <v>0.29950887865984649</v>
+        <v>0.29931147060062552</v>
       </c>
       <c r="N139">
         <v>5</v>
@@ -22838,7 +22842,7 @@
         <v>1.4E-2</v>
       </c>
       <c r="AA139">
-        <v>0.1304432828376792</v>
+        <v>0.13044328283767923</v>
       </c>
       <c r="AB139">
         <v>4</v>
@@ -22873,10 +22877,10 @@
         <v>960</v>
       </c>
       <c r="L140">
-        <v>19.516500000000001</v>
+        <v>10.228816221697572</v>
       </c>
       <c r="M140">
-        <v>0.29922322973963922</v>
+        <v>0.29918487785413445</v>
       </c>
       <c r="N140">
         <v>4</v>
@@ -22912,7 +22916,7 @@
         <v>3.7694999999999999</v>
       </c>
       <c r="AA140">
-        <v>0.12234006826129726</v>
+        <v>0.12234006826129734</v>
       </c>
       <c r="AB140">
         <v>3</v>
@@ -22947,10 +22951,10 @@
         <v>960</v>
       </c>
       <c r="L141">
-        <v>22.702500000000001</v>
+        <v>14.253087863140561</v>
       </c>
       <c r="M141">
-        <v>0.29117936449040921</v>
+        <v>0.29113078894601502</v>
       </c>
       <c r="N141">
         <v>1</v>
@@ -22986,7 +22990,7 @@
         <v>0.1295</v>
       </c>
       <c r="AA141">
-        <v>0.1212069997630716</v>
+        <v>0.1212069997630717</v>
       </c>
       <c r="AB141">
         <v>4</v>
@@ -23021,10 +23025,10 @@
         <v>960</v>
       </c>
       <c r="L142">
-        <v>15.827999999999999</v>
+        <v>8.8600135930610815</v>
       </c>
       <c r="M142">
-        <v>0.29048458309255032</v>
+        <v>0.29055754819549129</v>
       </c>
       <c r="N142">
         <v>2</v>
@@ -23060,7 +23064,7 @@
         <v>0.56699999999999995</v>
       </c>
       <c r="AA142">
-        <v>0.1212048945565416</v>
+        <v>0.1212048945565417</v>
       </c>
       <c r="AB142">
         <v>5</v>
@@ -23095,10 +23099,10 @@
         <v>960</v>
       </c>
       <c r="L143">
-        <v>22.052250000000001</v>
+        <v>10.071719679970638</v>
       </c>
       <c r="M143">
-        <v>0.28991087769702972</v>
+        <v>0.28993943313442189</v>
       </c>
       <c r="N143">
         <v>5</v>
@@ -23169,10 +23173,10 @@
         <v>960</v>
       </c>
       <c r="L144">
-        <v>18.1995</v>
+        <v>9.6143409574455259</v>
       </c>
       <c r="M144">
-        <v>0.28890766533143475</v>
+        <v>0.28892750750673424</v>
       </c>
       <c r="N144">
         <v>3</v>
@@ -23243,10 +23247,10 @@
         <v>960</v>
       </c>
       <c r="L145">
-        <v>11.24625</v>
+        <v>5.6200428381229139</v>
       </c>
       <c r="M145">
-        <v>0.28684983887332088</v>
+        <v>0.28688248552675655</v>
       </c>
       <c r="N145">
         <v>4</v>
@@ -23317,10 +23321,10 @@
         <v>960</v>
       </c>
       <c r="L146">
-        <v>15.069750000000001</v>
+        <v>6.960495415555024</v>
       </c>
       <c r="M146">
-        <v>0.28176241336161584</v>
+        <v>0.28169108346867922</v>
       </c>
       <c r="N146">
         <v>5</v>
@@ -23391,10 +23395,10 @@
         <v>960</v>
       </c>
       <c r="L147">
-        <v>31.835999999999999</v>
+        <v>19.694442152995169</v>
       </c>
       <c r="M147">
-        <v>0.28081580006591189</v>
+        <v>0.2808665322101776</v>
       </c>
       <c r="N147">
         <v>1</v>
@@ -23465,10 +23469,10 @@
         <v>960</v>
       </c>
       <c r="L148">
-        <v>14.183999999999999</v>
+        <v>7.9226322475051791</v>
       </c>
       <c r="M148">
-        <v>0.28048449271530418</v>
+        <v>0.28051769310715419</v>
       </c>
       <c r="N148">
         <v>3</v>
@@ -23504,7 +23508,7 @@
         <v>0.10150000000000001</v>
       </c>
       <c r="AA148">
-        <v>0.1085451568175837</v>
+        <v>0.1085451568175838</v>
       </c>
       <c r="AB148">
         <v>2</v>
@@ -23539,10 +23543,10 @@
         <v>960</v>
       </c>
       <c r="L149">
-        <v>19.522500000000001</v>
+        <v>11.546605749131857</v>
       </c>
       <c r="M149">
-        <v>0.27902425317829177</v>
+        <v>0.27899244600605116</v>
       </c>
       <c r="N149">
         <v>2</v>
@@ -23578,7 +23582,7 @@
         <v>4.5010000000000003</v>
       </c>
       <c r="AA149">
-        <v>0.10529122595398191</v>
+        <v>0.10529122595398192</v>
       </c>
       <c r="AB149">
         <v>1</v>
@@ -23613,10 +23617,10 @@
         <v>960</v>
       </c>
       <c r="L150">
-        <v>27.93525</v>
+        <v>13.338287903937522</v>
       </c>
       <c r="M150">
-        <v>0.27853542439954676</v>
+        <v>0.27855642685060766</v>
       </c>
       <c r="N150">
         <v>4</v>
@@ -23687,10 +23691,10 @@
         <v>960</v>
       </c>
       <c r="L151">
-        <v>24.632249999999999</v>
+        <v>15.546357365934561</v>
       </c>
       <c r="M151">
-        <v>0.27090969568401063</v>
+        <v>0.27090225796553097</v>
       </c>
       <c r="N151">
         <v>1</v>
@@ -23726,7 +23730,7 @@
         <v>8.9249999999999996E-2</v>
       </c>
       <c r="AA151">
-        <v>0.1029070119653622</v>
+        <v>0.1029070119653623</v>
       </c>
       <c r="AB151">
         <v>4</v>
@@ -23761,10 +23765,10 @@
         <v>960</v>
       </c>
       <c r="L152">
-        <v>14.40375</v>
+        <v>8.2780760568311571</v>
       </c>
       <c r="M152">
-        <v>0.26954291497469895</v>
+        <v>0.26956687577740635</v>
       </c>
       <c r="N152">
         <v>2</v>
@@ -23835,10 +23839,10 @@
         <v>960</v>
       </c>
       <c r="L153">
-        <v>28.138500000000001</v>
+        <v>14.438477401707292</v>
       </c>
       <c r="M153">
-        <v>0.26926825447120589</v>
+        <v>0.26921798427526988</v>
       </c>
       <c r="N153">
         <v>4</v>
@@ -23874,7 +23878,7 @@
         <v>1.071</v>
       </c>
       <c r="AA153">
-        <v>9.7513089312997805E-2</v>
+        <v>9.7513089312997903E-2</v>
       </c>
       <c r="AB153">
         <v>2</v>
@@ -23909,10 +23913,10 @@
         <v>960</v>
       </c>
       <c r="L154">
-        <v>22.53</v>
+        <v>12.314013015534112</v>
       </c>
       <c r="M154">
-        <v>0.26921519747623063</v>
+        <v>0.26906548918142209</v>
       </c>
       <c r="N154">
         <v>3</v>
@@ -23948,7 +23952,7 @@
         <v>4.1737500000000001</v>
       </c>
       <c r="AA154">
-        <v>9.2862603636383489E-2</v>
+        <v>9.2862603636383587E-2</v>
       </c>
       <c r="AB154">
         <v>2</v>
@@ -23983,10 +23987,10 @@
         <v>960</v>
       </c>
       <c r="L155">
-        <v>36.944249999999997</v>
+        <v>15.828233100452723</v>
       </c>
       <c r="M155">
-        <v>0.2687362578503053</v>
+        <v>0.26875647229873917</v>
       </c>
       <c r="N155">
         <v>5</v>
@@ -24022,7 +24026,7 @@
         <v>4.725E-2</v>
       </c>
       <c r="AA155">
-        <v>9.1342075028452097E-2</v>
+        <v>9.1342075028452208E-2</v>
       </c>
       <c r="AB155">
         <v>5</v>
@@ -24057,10 +24061,10 @@
         <v>960</v>
       </c>
       <c r="L156">
-        <v>13.45125</v>
+        <v>8.5783544124383564</v>
       </c>
       <c r="M156">
-        <v>0.26092773655799911</v>
+        <v>0.26118529137170937</v>
       </c>
       <c r="N156">
         <v>1</v>
@@ -24096,7 +24100,7 @@
         <v>1.95825</v>
       </c>
       <c r="AA156">
-        <v>9.030736556050846E-2</v>
+        <v>9.0307365560508571E-2</v>
       </c>
       <c r="AB156">
         <v>1</v>
@@ -24131,10 +24135,10 @@
         <v>960</v>
       </c>
       <c r="L157">
-        <v>25.029</v>
+        <v>14.109843005978622</v>
       </c>
       <c r="M157">
-        <v>0.26025507573355128</v>
+        <v>0.26013432279500248</v>
       </c>
       <c r="N157">
         <v>2</v>
@@ -24170,7 +24174,7 @@
         <v>3.4562499999999998</v>
       </c>
       <c r="AA157">
-        <v>8.9602905375267106E-2</v>
+        <v>8.9602905375267217E-2</v>
       </c>
       <c r="AB157">
         <v>3</v>
@@ -24205,10 +24209,10 @@
         <v>960</v>
       </c>
       <c r="L158">
-        <v>20.748750000000001</v>
+        <v>9.7580320647246914</v>
       </c>
       <c r="M158">
-        <v>0.26010267418659411</v>
+        <v>0.26010796493667482</v>
       </c>
       <c r="N158">
         <v>4</v>
@@ -24279,10 +24283,10 @@
         <v>960</v>
       </c>
       <c r="L159">
-        <v>18.93975</v>
+        <v>9.6872816895110549</v>
       </c>
       <c r="M159">
-        <v>0.25957441406123755</v>
+        <v>0.25961940830288999</v>
       </c>
       <c r="N159">
         <v>3</v>
@@ -24353,10 +24357,10 @@
         <v>960</v>
       </c>
       <c r="L160">
-        <v>28.2285</v>
+        <v>12.24162637204104</v>
       </c>
       <c r="M160">
-        <v>0.25872057099993184</v>
+        <v>0.25876383671813108</v>
       </c>
       <c r="N160">
         <v>5</v>
@@ -24427,10 +24431,10 @@
         <v>960</v>
       </c>
       <c r="L161">
-        <v>23.35425</v>
+        <v>11.19569713809679</v>
       </c>
       <c r="M161">
-        <v>0.25178062340667856</v>
+        <v>0.25178040242009903</v>
       </c>
       <c r="N161">
         <v>4</v>
@@ -24466,7 +24470,7 @@
         <v>0.49175000000000002</v>
       </c>
       <c r="AA161">
-        <v>8.2309622160488705E-2</v>
+        <v>8.2309622160488802E-2</v>
       </c>
       <c r="AB161">
         <v>2</v>
@@ -24501,10 +24505,10 @@
         <v>960</v>
       </c>
       <c r="L162">
-        <v>18.1035</v>
+        <v>10.727933222328229</v>
       </c>
       <c r="M162">
-        <v>0.25131163722612243</v>
+        <v>0.25131926056252685</v>
       </c>
       <c r="N162">
         <v>1</v>
@@ -24540,7 +24544,7 @@
         <v>3.5000000000000001E-3</v>
       </c>
       <c r="AA162">
-        <v>8.1637198442525497E-2</v>
+        <v>8.1637198442525594E-2</v>
       </c>
       <c r="AB162">
         <v>5</v>
@@ -24575,10 +24579,10 @@
         <v>960</v>
       </c>
       <c r="L163">
-        <v>15.5205</v>
+        <v>9.3672730461392728</v>
       </c>
       <c r="M163">
-        <v>0.24951556657559854</v>
+        <v>0.2495385424015589</v>
       </c>
       <c r="N163">
         <v>2</v>
@@ -24649,10 +24653,10 @@
         <v>960</v>
       </c>
       <c r="L164">
-        <v>18.403500000000001</v>
+        <v>9.6720552243298936</v>
       </c>
       <c r="M164">
-        <v>0.24847976754738862</v>
+        <v>0.24852978594473921</v>
       </c>
       <c r="N164">
         <v>3</v>
@@ -24688,7 +24692,7 @@
         <v>2.3414999999999999</v>
       </c>
       <c r="AA164">
-        <v>7.1389472178539526E-2</v>
+        <v>7.1389472178539595E-2</v>
       </c>
       <c r="AB164">
         <v>2</v>
@@ -24723,10 +24727,10 @@
         <v>960</v>
       </c>
       <c r="L165">
-        <v>26.224499999999999</v>
+        <v>10.325300396264383</v>
       </c>
       <c r="M165">
-        <v>0.24838423111010824</v>
+        <v>0.24837914159496388</v>
       </c>
       <c r="N165">
         <v>5</v>
@@ -24797,10 +24801,10 @@
         <v>960</v>
       </c>
       <c r="L166">
-        <v>22.263750000000002</v>
+        <v>12.784071041012059</v>
       </c>
       <c r="M166">
-        <v>0.24072196893523218</v>
+        <v>0.24095352618805257</v>
       </c>
       <c r="N166">
         <v>2</v>
@@ -24836,7 +24840,7 @@
         <v>1.7290000000000001</v>
       </c>
       <c r="AA166">
-        <v>6.8339338270038366E-2</v>
+        <v>6.8339338270038436E-2</v>
       </c>
       <c r="AB166">
         <v>1</v>
@@ -24871,10 +24875,10 @@
         <v>960</v>
       </c>
       <c r="L167">
-        <v>20.833500000000001</v>
+        <v>11.822446140722629</v>
       </c>
       <c r="M167">
-        <v>0.24069298780785864</v>
+        <v>0.240644775748169</v>
       </c>
       <c r="N167">
         <v>1</v>
@@ -24910,7 +24914,7 @@
         <v>3.5122499999999999</v>
       </c>
       <c r="AA167">
-        <v>6.7065660518415698E-2</v>
+        <v>6.7065660518415796E-2</v>
       </c>
       <c r="AB167">
         <v>4</v>
@@ -24945,10 +24949,10 @@
         <v>960</v>
       </c>
       <c r="L168">
-        <v>29.264250000000001</v>
+        <v>12.65509793005895</v>
       </c>
       <c r="M168">
-        <v>0.23986147209538583</v>
+        <v>0.23980956195027237</v>
       </c>
       <c r="N168">
         <v>4</v>
@@ -25019,10 +25023,10 @@
         <v>960</v>
       </c>
       <c r="L169">
-        <v>30.54</v>
+        <v>12.197718308228682</v>
       </c>
       <c r="M169">
-        <v>0.23946768352858208</v>
+        <v>0.2395348412698213</v>
       </c>
       <c r="N169">
         <v>5</v>
@@ -25093,10 +25097,10 @@
         <v>960</v>
       </c>
       <c r="L170">
-        <v>12.273</v>
+        <v>6.104821218550863</v>
       </c>
       <c r="M170">
-        <v>0.23935265173697259</v>
+        <v>0.23936592685086922</v>
       </c>
       <c r="N170">
         <v>3</v>
@@ -25167,10 +25171,10 @@
         <v>960</v>
       </c>
       <c r="L171">
-        <v>31.949249999999999</v>
+        <v>17.815987424419255</v>
       </c>
       <c r="M171">
-        <v>0.2312020828081526</v>
+        <v>0.23120389540852757</v>
       </c>
       <c r="N171">
         <v>2</v>
@@ -25241,10 +25245,10 @@
         <v>960</v>
       </c>
       <c r="L172">
-        <v>22.02525</v>
+        <v>12.259376185645555</v>
       </c>
       <c r="M172">
-        <v>0.23051363063462801</v>
+        <v>0.23049039651497236</v>
       </c>
       <c r="N172">
         <v>1</v>
@@ -25315,10 +25319,10 @@
         <v>960</v>
       </c>
       <c r="L173">
-        <v>35.413499999999999</v>
+        <v>13.925043029569689</v>
       </c>
       <c r="M173">
-        <v>0.23049004263284281</v>
+        <v>0.23041473371000601</v>
       </c>
       <c r="N173">
         <v>5</v>
@@ -25354,7 +25358,7 @@
         <v>6.6150000000000002</v>
       </c>
       <c r="AA173">
-        <v>5.7088602459741254E-2</v>
+        <v>5.7088602459741261E-2</v>
       </c>
       <c r="AB173">
         <v>2</v>
@@ -25389,10 +25393,10 @@
         <v>960</v>
       </c>
       <c r="L174">
-        <v>36.423000000000002</v>
+        <v>17.062664284678625</v>
       </c>
       <c r="M174">
-        <v>0.22989307530051598</v>
+        <v>0.22985232227407917</v>
       </c>
       <c r="N174">
         <v>3</v>
@@ -25463,10 +25467,10 @@
         <v>960</v>
       </c>
       <c r="L175">
-        <v>13.426500000000001</v>
+        <v>6.183163472814396</v>
       </c>
       <c r="M175">
-        <v>0.22979188093128161</v>
+        <v>0.22975232600855888</v>
       </c>
       <c r="N175">
         <v>4</v>
@@ -25537,10 +25541,10 @@
         <v>960</v>
       </c>
       <c r="L176">
-        <v>18.074999999999999</v>
+        <v>10.755964998050276</v>
       </c>
       <c r="M176">
-        <v>0.22219681132726954</v>
+        <v>0.22219712235422656</v>
       </c>
       <c r="N176">
         <v>1</v>
@@ -25611,10 +25615,10 @@
         <v>960</v>
       </c>
       <c r="L177">
-        <v>24.38475</v>
+        <v>12.365150374397457</v>
       </c>
       <c r="M177">
-        <v>0.22209547766636631</v>
+        <v>0.22209516048236241</v>
       </c>
       <c r="N177">
         <v>3</v>
@@ -25685,10 +25689,10 @@
         <v>960</v>
       </c>
       <c r="L178">
-        <v>39.093000000000004</v>
+        <v>15.54996614829142</v>
       </c>
       <c r="M178">
-        <v>0.22030939766869767</v>
+        <v>0.22026034375492762</v>
       </c>
       <c r="N178">
         <v>5</v>
@@ -25759,10 +25763,10 @@
         <v>960</v>
       </c>
       <c r="L179">
-        <v>14.231249999999999</v>
+        <v>8.3091880438005656</v>
       </c>
       <c r="M179">
-        <v>0.21973757682912101</v>
+        <v>0.2195863829821553</v>
       </c>
       <c r="N179">
         <v>2</v>
@@ -25833,10 +25837,10 @@
         <v>960</v>
       </c>
       <c r="L180">
-        <v>32.34225</v>
+        <v>14.302460027037997</v>
       </c>
       <c r="M180">
-        <v>0.2195823944577287</v>
+        <v>0.21957376469826825</v>
       </c>
       <c r="N180">
         <v>4</v>
@@ -25907,10 +25911,10 @@
         <v>960</v>
       </c>
       <c r="L181">
-        <v>31.31325</v>
+        <v>18.210500258570359</v>
       </c>
       <c r="M181">
-        <v>0.21240373616349439</v>
+        <v>0.21244974532189095</v>
       </c>
       <c r="N181">
         <v>1</v>
@@ -25981,10 +25985,10 @@
         <v>960</v>
       </c>
       <c r="L182">
-        <v>21.9495</v>
+        <v>11.064353590812187</v>
       </c>
       <c r="M182">
-        <v>0.21134159361012633</v>
+        <v>0.21131762613112975</v>
       </c>
       <c r="N182">
         <v>3</v>
@@ -26020,7 +26024,7 @@
         <v>2.2697500000000002</v>
       </c>
       <c r="AA182">
-        <v>2.8741620246962397E-2</v>
+        <v>2.8741620246962474E-2</v>
       </c>
       <c r="AB182">
         <v>2</v>
@@ -26055,10 +26059,10 @@
         <v>960</v>
       </c>
       <c r="L183">
-        <v>30.016500000000001</v>
+        <v>15.46511774629367</v>
       </c>
       <c r="M183">
-        <v>0.21075321225494284</v>
+        <v>0.21079015445168753</v>
       </c>
       <c r="N183">
         <v>2</v>
@@ -26129,10 +26133,10 @@
         <v>960</v>
       </c>
       <c r="L184">
-        <v>17.61525</v>
+        <v>8.1563445984862302</v>
       </c>
       <c r="M184">
-        <v>0.21002888063135774</v>
+        <v>0.20998918597093627</v>
       </c>
       <c r="N184">
         <v>4</v>
@@ -26203,10 +26207,10 @@
         <v>960</v>
       </c>
       <c r="L185">
-        <v>24.818249999999999</v>
+        <v>9.9918547275539815</v>
       </c>
       <c r="M185">
-        <v>0.20952870035320914</v>
+        <v>0.20962857191636675</v>
       </c>
       <c r="N185">
         <v>5</v>
@@ -26242,7 +26246,7 @@
         <v>1.1165</v>
       </c>
       <c r="AA185">
-        <v>2.1628354220990999E-2</v>
+        <v>2.1628354220991099E-2</v>
       </c>
       <c r="AB185">
         <v>2</v>
@@ -26277,10 +26281,10 @@
         <v>960</v>
       </c>
       <c r="L186">
-        <v>23.516249999999999</v>
+        <v>10.292976941548543</v>
       </c>
       <c r="M186">
-        <v>0.20105539456805072</v>
+        <v>0.20102883321305007</v>
       </c>
       <c r="N186">
         <v>4</v>
@@ -26351,10 +26355,10 @@
         <v>960</v>
       </c>
       <c r="L187">
-        <v>20.192250000000001</v>
+        <v>7.8359042189439325</v>
       </c>
       <c r="M187">
-        <v>0.20092971754481859</v>
+        <v>0.20092658461954235</v>
       </c>
       <c r="N187">
         <v>5</v>
@@ -26425,10 +26429,10 @@
         <v>960</v>
       </c>
       <c r="L188">
-        <v>38.191499999999998</v>
+        <v>21.871443842368283</v>
       </c>
       <c r="M188">
-        <v>0.19996625114563701</v>
+        <v>0.19995321089879223</v>
       </c>
       <c r="N188">
         <v>1</v>
@@ -26463,10 +26467,10 @@
         <v>960</v>
       </c>
       <c r="L189">
-        <v>35.077500000000001</v>
+        <v>18.604141341855126</v>
       </c>
       <c r="M189">
-        <v>0.19981946200664891</v>
+        <v>0.1996500651016114</v>
       </c>
       <c r="N189">
         <v>2</v>
@@ -26501,10 +26505,10 @@
         <v>960</v>
       </c>
       <c r="L190">
-        <v>30.809249999999999</v>
+        <v>14.728293239057878</v>
       </c>
       <c r="M190">
-        <v>0.19866194642778132</v>
+        <v>0.19869053888880714</v>
       </c>
       <c r="N190">
         <v>3</v>
@@ -26539,10 +26543,10 @@
         <v>960</v>
       </c>
       <c r="L191">
-        <v>22.003499999999999</v>
+        <v>9.3461776554808704</v>
       </c>
       <c r="M191">
-        <v>0.191258779885733</v>
+        <v>0.19137833545123181</v>
       </c>
       <c r="N191">
         <v>4</v>
@@ -26577,10 +26581,10 @@
         <v>960</v>
       </c>
       <c r="L192">
-        <v>33.993000000000002</v>
+        <v>18.390595323627593</v>
       </c>
       <c r="M192">
-        <v>0.19104530876520678</v>
+        <v>0.19101169184477446</v>
       </c>
       <c r="N192">
         <v>1</v>
@@ -26615,10 +26619,10 @@
         <v>960</v>
       </c>
       <c r="L193">
-        <v>37.607250000000001</v>
+        <v>17.673137365200162</v>
       </c>
       <c r="M193">
-        <v>0.19002622686881221</v>
+        <v>0.19005513759475884</v>
       </c>
       <c r="N193">
         <v>2</v>
@@ -26653,10 +26657,10 @@
         <v>960</v>
       </c>
       <c r="L194">
-        <v>29.459250000000001</v>
+        <v>13.233843941124571</v>
       </c>
       <c r="M194">
-        <v>0.18962388338576786</v>
+        <v>0.18954840669509374</v>
       </c>
       <c r="N194">
         <v>3</v>
@@ -26691,10 +26695,10 @@
         <v>960</v>
       </c>
       <c r="L195">
-        <v>17.696999999999999</v>
+        <v>6.6724004479142494</v>
       </c>
       <c r="M195">
-        <v>0.18885111827548984</v>
+        <v>0.18892991429401532</v>
       </c>
       <c r="N195">
         <v>5</v>
@@ -26729,10 +26733,10 @@
         <v>960</v>
       </c>
       <c r="L196">
-        <v>25.614000000000001</v>
+        <v>12.998531711683478</v>
       </c>
       <c r="M196">
-        <v>0.18117725446254437</v>
+        <v>0.18126355333903593</v>
       </c>
       <c r="N196">
         <v>2</v>
@@ -26767,10 +26771,10 @@
         <v>960</v>
       </c>
       <c r="L197">
-        <v>17.690249999999999</v>
+        <v>6.688938926698567</v>
       </c>
       <c r="M197">
-        <v>0.17993909992720603</v>
+        <v>0.17994862646671878</v>
       </c>
       <c r="N197">
         <v>5</v>
@@ -26805,10 +26809,10 @@
         <v>960</v>
       </c>
       <c r="L198">
-        <v>24.443999999999999</v>
+        <v>10.526445408296755</v>
       </c>
       <c r="M198">
-        <v>0.17983127674066524</v>
+        <v>0.17987115348662197</v>
       </c>
       <c r="N198">
         <v>4</v>
@@ -26843,10 +26847,10 @@
         <v>960</v>
       </c>
       <c r="L199">
-        <v>20.498999999999999</v>
+        <v>8.7861407868959081</v>
       </c>
       <c r="M199">
-        <v>0.17947724617378755</v>
+        <v>0.17951013560156492</v>
       </c>
       <c r="N199">
         <v>3</v>
@@ -26881,10 +26885,10 @@
         <v>960</v>
       </c>
       <c r="L200">
-        <v>34.398000000000003</v>
+        <v>18.824509323408478</v>
       </c>
       <c r="M200">
-        <v>0.17899842378213915</v>
+        <v>0.17910762298145519</v>
       </c>
       <c r="N200">
         <v>1</v>
@@ -26919,10 +26923,10 @@
         <v>960</v>
       </c>
       <c r="L201">
-        <v>41.15925</v>
+        <v>21.327911803886831</v>
       </c>
       <c r="M201">
-        <v>0.17068842234520554</v>
+        <v>0.17077472774120292</v>
       </c>
       <c r="N201">
         <v>1</v>
@@ -26957,10 +26961,10 @@
         <v>960</v>
       </c>
       <c r="L202">
-        <v>50.739750000000001</v>
+        <v>24.813622100566811</v>
       </c>
       <c r="M202">
-        <v>0.17004532510630618</v>
+        <v>0.16992942313658874</v>
       </c>
       <c r="N202">
         <v>2</v>
@@ -26995,10 +26999,10 @@
         <v>960</v>
       </c>
       <c r="L203">
-        <v>20.928000000000001</v>
+        <v>8.3122118312066569</v>
       </c>
       <c r="M203">
-        <v>0.16969990322126663</v>
+        <v>0.16972094836974569</v>
       </c>
       <c r="N203">
         <v>4</v>
@@ -27033,10 +27037,10 @@
         <v>960</v>
       </c>
       <c r="L204">
-        <v>27.7575</v>
+        <v>11.732910160473644</v>
       </c>
       <c r="M204">
-        <v>0.16914513295113398</v>
+        <v>0.16917524141389684</v>
       </c>
       <c r="N204">
         <v>3</v>
@@ -27071,10 +27075,10 @@
         <v>960</v>
       </c>
       <c r="L205">
-        <v>19.96275</v>
+        <v>7.4015492372206886</v>
       </c>
       <c r="M205">
-        <v>0.16835732939881609</v>
+        <v>0.16836334089647703</v>
       </c>
       <c r="N205">
         <v>5</v>
@@ -27109,10 +27113,10 @@
         <v>960</v>
       </c>
       <c r="L206">
-        <v>9.3795000000000002</v>
+        <v>3.5987155404272682</v>
       </c>
       <c r="M206">
-        <v>0.16124405045929022</v>
+        <v>0.16115608866144257</v>
       </c>
       <c r="N206">
         <v>5</v>
@@ -27147,10 +27151,10 @@
         <v>960</v>
       </c>
       <c r="L207">
-        <v>26.760750000000002</v>
+        <v>14.15051948002926</v>
       </c>
       <c r="M207">
-        <v>0.16033867977595728</v>
+        <v>0.1604881866514922</v>
       </c>
       <c r="N207">
         <v>1</v>
@@ -27185,10 +27189,10 @@
         <v>960</v>
       </c>
       <c r="L208">
-        <v>39.85125</v>
+        <v>18.536203287816438</v>
       </c>
       <c r="M208">
-        <v>0.15998336690116838</v>
+        <v>0.15997410044309562</v>
       </c>
       <c r="N208">
         <v>2</v>
@@ -27223,10 +27227,10 @@
         <v>960</v>
       </c>
       <c r="L209">
-        <v>46.743000000000002</v>
+        <v>20.23026662912217</v>
       </c>
       <c r="M209">
-        <v>0.15943280659374451</v>
+        <v>0.15952866796156623</v>
       </c>
       <c r="N209">
         <v>3</v>
@@ -27261,10 +27265,10 @@
         <v>960</v>
       </c>
       <c r="L210">
-        <v>26.596499999999999</v>
+        <v>10.857948028775041</v>
       </c>
       <c r="M210">
-        <v>0.15835226301937044</v>
+        <v>0.15843381059849124</v>
       </c>
       <c r="N210">
         <v>4</v>
@@ -27299,10 +27303,10 @@
         <v>960</v>
       </c>
       <c r="L211">
-        <v>28.331250000000001</v>
+        <v>10.950794054390228</v>
       </c>
       <c r="M211">
-        <v>0.15153943492360553</v>
+        <v>0.15152629131103196</v>
       </c>
       <c r="N211">
         <v>5</v>
@@ -27337,10 +27341,10 @@
         <v>960</v>
       </c>
       <c r="L212">
-        <v>30.64425</v>
+        <v>12.669790603860866</v>
       </c>
       <c r="M212">
-        <v>0.15095870880566087</v>
+        <v>0.15092332220504603</v>
       </c>
       <c r="N212">
         <v>4</v>
@@ -27375,10 +27379,10 @@
         <v>960</v>
       </c>
       <c r="L213">
-        <v>39.533999999999999</v>
+        <v>18.006809306073539</v>
       </c>
       <c r="M213">
-        <v>0.14972450251373012</v>
+        <v>0.14979527589067945</v>
       </c>
       <c r="N213">
         <v>3</v>
@@ -27413,10 +27417,10 @@
         <v>960</v>
       </c>
       <c r="L214">
-        <v>39.881999999999998</v>
+        <v>20.969888167026415</v>
       </c>
       <c r="M214">
-        <v>0.14945488524032777</v>
+        <v>0.14944064793348052</v>
       </c>
       <c r="N214">
         <v>2</v>
@@ -27451,10 +27455,10 @@
         <v>960</v>
       </c>
       <c r="L215">
-        <v>18.298500000000001</v>
+        <v>11.127326614185408</v>
       </c>
       <c r="M215">
-        <v>0.14819006447890185</v>
+        <v>0.14833344854093691</v>
       </c>
       <c r="N215">
         <v>1</v>
@@ -27489,10 +27493,10 @@
         <v>960</v>
       </c>
       <c r="L216">
-        <v>23.792249999999999</v>
+        <v>12.532801701707427</v>
       </c>
       <c r="M216">
-        <v>0.14159448997863108</v>
+        <v>0.14147976678390659</v>
       </c>
       <c r="N216">
         <v>1</v>
@@ -27527,10 +27531,10 @@
         <v>960</v>
       </c>
       <c r="L217">
-        <v>17.411249999999999</v>
+        <v>6.6738230348596685</v>
       </c>
       <c r="M217">
-        <v>0.1409053983830009</v>
+        <v>0.14087857954216845</v>
       </c>
       <c r="N217">
         <v>5</v>
@@ -27565,10 +27569,10 @@
         <v>960</v>
       </c>
       <c r="L218">
-        <v>40.520249999999997</v>
+        <v>18.999554426754099</v>
       </c>
       <c r="M218">
-        <v>0.14051224566306653</v>
+        <v>0.14057849094976485</v>
       </c>
       <c r="N218">
         <v>2</v>
@@ -27603,10 +27607,10 @@
         <v>960</v>
       </c>
       <c r="L219">
-        <v>32.659500000000001</v>
+        <v>15.200611850239344</v>
       </c>
       <c r="M219">
-        <v>0.14011069948176805</v>
+        <v>0.14043141067793805</v>
       </c>
       <c r="N219">
         <v>3</v>
@@ -27641,10 +27645,10 @@
         <v>960</v>
       </c>
       <c r="L220">
-        <v>24.806249999999999</v>
+        <v>10.213770624390266</v>
       </c>
       <c r="M220">
-        <v>0.13921947695286924</v>
+        <v>0.1391634575045976</v>
       </c>
       <c r="N220">
         <v>4</v>
@@ -27679,10 +27683,10 @@
         <v>960</v>
       </c>
       <c r="L221">
-        <v>8.3512500000000003</v>
+        <v>3.2146885428855052</v>
       </c>
       <c r="M221">
-        <v>0.13228693715556963</v>
+        <v>0.13221364625852378</v>
       </c>
       <c r="N221">
         <v>5</v>
@@ -27717,10 +27721,10 @@
         <v>960</v>
       </c>
       <c r="L222">
-        <v>27.449249999999999</v>
+        <v>12.931567218934568</v>
       </c>
       <c r="M222">
-        <v>0.13104108689205315</v>
+        <v>0.1310315846396341</v>
       </c>
       <c r="N222">
         <v>2</v>
@@ -27755,10 +27759,10 @@
         <v>960</v>
       </c>
       <c r="L223">
-        <v>26.076750000000001</v>
+        <v>11.008035447095738</v>
       </c>
       <c r="M223">
-        <v>0.13065518621763961</v>
+        <v>0.13064851481305476</v>
       </c>
       <c r="N223">
         <v>4</v>
@@ -27793,10 +27797,10 @@
         <v>960</v>
       </c>
       <c r="L224">
-        <v>6.0187499999999998</v>
+        <v>4.0790523720854193</v>
       </c>
       <c r="M224">
-        <v>0.12990539932330603</v>
+        <v>0.12955727884432983</v>
       </c>
       <c r="N224">
         <v>1</v>
@@ -27831,10 +27835,10 @@
         <v>960</v>
       </c>
       <c r="L225">
-        <v>30.537749999999999</v>
+        <v>14.853025317896886</v>
       </c>
       <c r="M225">
-        <v>0.12876600210812941</v>
+        <v>0.12878574479738653</v>
       </c>
       <c r="N225">
         <v>3</v>
@@ -27869,10 +27873,10 @@
         <v>960</v>
       </c>
       <c r="L226">
-        <v>28.551749999999998</v>
+        <v>16.038566130030297</v>
       </c>
       <c r="M226">
-        <v>0.12169118919107791</v>
+        <v>0.12164028079470092</v>
       </c>
       <c r="N226">
         <v>1</v>
@@ -27907,10 +27911,10 @@
         <v>960</v>
       </c>
       <c r="L227">
-        <v>19.087499999999999</v>
+        <v>7.4580449175934058</v>
       </c>
       <c r="M227">
-        <v>0.12074954537778694</v>
+        <v>0.12077554097886234</v>
       </c>
       <c r="N227">
         <v>5</v>
@@ -27945,10 +27949,10 @@
         <v>960</v>
       </c>
       <c r="L228">
-        <v>27.867750000000001</v>
+        <v>11.868824474430726</v>
       </c>
       <c r="M228">
-        <v>0.120212023466233</v>
+        <v>0.1201807733557297</v>
       </c>
       <c r="N228">
         <v>4</v>
@@ -27983,10 +27987,10 @@
         <v>960</v>
       </c>
       <c r="L229">
-        <v>29.758500000000002</v>
+        <v>15.160638350933434</v>
       </c>
       <c r="M229">
-        <v>0.11993249887182912</v>
+        <v>0.11978055646195693</v>
       </c>
       <c r="N229">
         <v>2</v>
@@ -28021,10 +28025,10 @@
         <v>960</v>
       </c>
       <c r="L230">
-        <v>36.195749999999997</v>
+        <v>16.302417159078569</v>
       </c>
       <c r="M230">
-        <v>0.11913968819059621</v>
+        <v>0.11907446231935563</v>
       </c>
       <c r="N230">
         <v>3</v>
@@ -28059,10 +28063,10 @@
         <v>960</v>
       </c>
       <c r="L231">
-        <v>32.003250000000001</v>
+        <v>17.842476562347095</v>
       </c>
       <c r="M231">
-        <v>0.11068809668643367</v>
+        <v>0.11050560243956452</v>
       </c>
       <c r="N231">
         <v>1</v>
@@ -28097,10 +28101,10 @@
         <v>960</v>
       </c>
       <c r="L232">
-        <v>42.534750000000003</v>
+        <v>20.155590984036618</v>
       </c>
       <c r="M232">
-        <v>0.11051207716444167</v>
+        <v>0.11043687878558224</v>
       </c>
       <c r="N232">
         <v>2</v>
@@ -28135,10 +28139,10 @@
         <v>960</v>
       </c>
       <c r="L233">
-        <v>38.740499999999997</v>
+        <v>16.870010334768434</v>
       </c>
       <c r="M233">
-        <v>0.11016529099058715</v>
+        <v>0.11023338202038008</v>
       </c>
       <c r="N233">
         <v>3</v>
@@ -28173,10 +28177,10 @@
         <v>960</v>
       </c>
       <c r="L234">
-        <v>40.990499999999997</v>
+        <v>16.838410038558653</v>
       </c>
       <c r="M234">
-        <v>0.11007823592813036</v>
+        <v>0.11006107057223617</v>
       </c>
       <c r="N234">
         <v>4</v>
@@ -28211,10 +28215,10 @@
         <v>960</v>
       </c>
       <c r="L235">
-        <v>22.8855</v>
+        <v>8.8021279837022899</v>
       </c>
       <c r="M235">
-        <v>0.11004208711742994</v>
+        <v>0.11003455637549028</v>
       </c>
       <c r="N235">
         <v>5</v>
@@ -28249,10 +28253,10 @@
         <v>960</v>
       </c>
       <c r="L236">
-        <v>24.102</v>
+        <v>10.259072785271528</v>
       </c>
       <c r="M236">
-        <v>0.10142000687156005</v>
+        <v>0.10143445260362567</v>
       </c>
       <c r="N236">
         <v>4</v>
@@ -28287,10 +28291,10 @@
         <v>960</v>
       </c>
       <c r="L237">
-        <v>28.248000000000001</v>
+        <v>12.264315637333736</v>
       </c>
       <c r="M237">
-        <v>0.10083103969611823</v>
+        <v>0.10088882094233406</v>
       </c>
       <c r="N237">
         <v>3</v>
@@ -28325,10 +28329,10 @@
         <v>960</v>
       </c>
       <c r="L238">
-        <v>36.515250000000002</v>
+        <v>16.981658885331559</v>
       </c>
       <c r="M238">
-        <v>9.9738262957887971E-2</v>
+        <v>9.9730553119249402E-2</v>
       </c>
       <c r="N238">
         <v>2</v>
@@ -28363,10 +28367,10 @@
         <v>960</v>
       </c>
       <c r="L239">
-        <v>20.116499999999998</v>
+        <v>10.369920926949888</v>
       </c>
       <c r="M239">
-        <v>9.9316157601408911E-2</v>
+        <v>9.9618067999867804E-2</v>
       </c>
       <c r="N239">
         <v>1</v>
@@ -28401,10 +28405,10 @@
         <v>960</v>
       </c>
       <c r="L240">
-        <v>15.906000000000001</v>
+        <v>6.5218004136377346</v>
       </c>
       <c r="M240">
-        <v>9.8775167049432275E-2</v>
+        <v>9.8920952386780434E-2</v>
       </c>
       <c r="N240">
         <v>5</v>
@@ -28439,10 +28443,10 @@
         <v>960</v>
       </c>
       <c r="L241">
-        <v>37.479750000000003</v>
+        <v>15.691407480767371</v>
       </c>
       <c r="M241">
-        <v>9.0687007109280113E-2</v>
+        <v>9.0609623062238714E-2</v>
       </c>
       <c r="N241">
         <v>3</v>
@@ -28477,10 +28481,10 @@
         <v>960</v>
       </c>
       <c r="L242">
-        <v>36.1905</v>
+        <v>19.240212817595662</v>
       </c>
       <c r="M242">
-        <v>9.0623592522372176E-2</v>
+        <v>9.0561803918215E-2</v>
       </c>
       <c r="N242">
         <v>1</v>
@@ -28515,10 +28519,10 @@
         <v>960</v>
       </c>
       <c r="L243">
-        <v>12.6195</v>
+        <v>5.0496467967045193</v>
       </c>
       <c r="M243">
-        <v>9.0339297084657308E-2</v>
+        <v>9.034540046305993E-2</v>
       </c>
       <c r="N243">
         <v>4</v>
@@ -28553,10 +28557,10 @@
         <v>960</v>
       </c>
       <c r="L244">
-        <v>37.640999999999998</v>
+        <v>19.039111567203648</v>
       </c>
       <c r="M244">
-        <v>8.9902189020644702E-2</v>
+        <v>9.0023066741246729E-2</v>
       </c>
       <c r="N244">
         <v>2</v>
@@ -28591,10 +28595,10 @@
         <v>960</v>
       </c>
       <c r="L245">
-        <v>15.52275</v>
+        <v>5.8518093207177193</v>
       </c>
       <c r="M245">
-        <v>8.9432008264741458E-2</v>
+        <v>8.9438611948001512E-2</v>
       </c>
       <c r="N245">
         <v>5</v>
@@ -28629,10 +28633,10 @@
         <v>960</v>
       </c>
       <c r="L246">
-        <v>29.294250000000002</v>
+        <v>12.803686332863636</v>
       </c>
       <c r="M246">
-        <v>8.0973614103841657E-2</v>
+        <v>8.1031913153139984E-2</v>
       </c>
       <c r="N246">
         <v>2</v>
@@ -28667,10 +28671,10 @@
         <v>960</v>
       </c>
       <c r="L247">
-        <v>25.67775</v>
+        <v>13.322722894589626</v>
       </c>
       <c r="M247">
-        <v>8.0346768723227657E-2</v>
+        <v>8.026729343605471E-2</v>
       </c>
       <c r="N247">
         <v>1</v>
@@ -28705,10 +28709,10 @@
         <v>960</v>
       </c>
       <c r="L248">
-        <v>20.43975</v>
+        <v>8.9647391501294322</v>
       </c>
       <c r="M248">
-        <v>8.0005251760022406E-2</v>
+        <v>7.9891704057924159E-2</v>
       </c>
       <c r="N248">
         <v>4</v>
@@ -28743,10 +28747,10 @@
         <v>960</v>
       </c>
       <c r="L249">
-        <v>11.037000000000001</v>
+        <v>4.3469625271393753</v>
       </c>
       <c r="M249">
-        <v>7.9714133564992753E-2</v>
+        <v>7.9746006727453508E-2</v>
       </c>
       <c r="N249">
         <v>5</v>
@@ -28781,10 +28785,10 @@
         <v>960</v>
       </c>
       <c r="L250">
-        <v>21.897749999999998</v>
+        <v>9.1144301166099506</v>
       </c>
       <c r="M250">
-        <v>7.9635056263665585E-2</v>
+        <v>7.9645012135613563E-2</v>
       </c>
       <c r="N250">
         <v>3</v>
@@ -28819,10 +28823,10 @@
         <v>960</v>
       </c>
       <c r="L251">
-        <v>21.699750000000002</v>
+        <v>9.0082838329265247</v>
       </c>
       <c r="M251">
-        <v>7.1701802992392052E-2</v>
+        <v>7.1691874509110451E-2</v>
       </c>
       <c r="N251">
         <v>3</v>
@@ -28857,10 +28861,10 @@
         <v>960</v>
       </c>
       <c r="L252">
-        <v>20.411249999999999</v>
+        <v>8.7700534933604217</v>
       </c>
       <c r="M252">
-        <v>7.0945983792338491E-2</v>
+        <v>7.0901125923973879E-2</v>
       </c>
       <c r="N252">
         <v>4</v>
@@ -28895,10 +28899,10 @@
         <v>960</v>
       </c>
       <c r="L253">
-        <v>14.000249999999999</v>
+        <v>6.6412865660033438</v>
       </c>
       <c r="M253">
-        <v>7.0459397428584231E-2</v>
+        <v>7.0583847899770069E-2</v>
       </c>
       <c r="N253">
         <v>2</v>
@@ -28933,10 +28937,10 @@
         <v>960</v>
       </c>
       <c r="L254">
-        <v>4.2802499999999997</v>
+        <v>1.695907922353193</v>
       </c>
       <c r="M254">
-        <v>7.0262684450367235E-2</v>
+        <v>7.0256570423061743E-2</v>
       </c>
       <c r="N254">
         <v>5</v>
@@ -28971,10 +28975,10 @@
         <v>960</v>
       </c>
       <c r="L255">
-        <v>17.850000000000001</v>
+        <v>10.321751756640623</v>
       </c>
       <c r="M255">
-        <v>6.9289725624725851E-2</v>
+        <v>6.9112823028192785E-2</v>
       </c>
       <c r="N255">
         <v>1</v>
@@ -29009,10 +29013,10 @@
         <v>960</v>
       </c>
       <c r="L256">
-        <v>7.3064999999999998</v>
+        <v>5.1147287865648963</v>
       </c>
       <c r="M256">
-        <v>6.1244619917841712E-2</v>
+        <v>6.1030273101421763E-2</v>
       </c>
       <c r="N256">
         <v>1</v>
@@ -29047,10 +29051,10 @@
         <v>960</v>
       </c>
       <c r="L257">
-        <v>12.499499999999999</v>
+        <v>4.9193484655090876</v>
       </c>
       <c r="M257">
-        <v>6.0895289428091894E-2</v>
+        <v>6.0909650016188151E-2</v>
       </c>
       <c r="N257">
         <v>5</v>
@@ -29085,10 +29089,10 @@
         <v>960</v>
       </c>
       <c r="L258">
-        <v>13.196999999999999</v>
+        <v>6.190179800201955</v>
       </c>
       <c r="M258">
-        <v>6.0715606907507755E-2</v>
+        <v>6.0739582843997039E-2</v>
       </c>
       <c r="N258">
         <v>2</v>
@@ -29123,10 +29127,10 @@
         <v>960</v>
       </c>
       <c r="L259">
-        <v>18.414750000000002</v>
+        <v>8.2471224810906438</v>
       </c>
       <c r="M259">
-        <v>6.05829979937937E-2</v>
+        <v>6.0386802147673689E-2</v>
       </c>
       <c r="N259">
         <v>3</v>
@@ -29161,10 +29165,10 @@
         <v>960</v>
       </c>
       <c r="L260">
-        <v>10.235250000000001</v>
+        <v>4.6143253887543452</v>
       </c>
       <c r="M260">
-        <v>5.8928017521810871E-2</v>
+        <v>5.8714285713278302E-2</v>
       </c>
       <c r="N260">
         <v>4</v>
@@ -29199,10 +29203,10 @@
         <v>960</v>
       </c>
       <c r="L261">
-        <v>9.8257499999999993</v>
+        <v>4.5601905472436952</v>
       </c>
       <c r="M261">
-        <v>5.0356035620682194E-2</v>
+        <v>5.0412151946954718E-2</v>
       </c>
       <c r="N261">
         <v>3</v>
@@ -29237,10 +29241,10 @@
         <v>960</v>
       </c>
       <c r="L262">
-        <v>8.8620000000000001</v>
+        <v>4.2243062230611601</v>
       </c>
       <c r="M262">
-        <v>5.0272053037651809E-2</v>
+        <v>5.0177486566320879E-2</v>
       </c>
       <c r="N262">
         <v>2</v>
@@ -29275,10 +29279,10 @@
         <v>960</v>
       </c>
       <c r="L263">
-        <v>1.92675</v>
+        <v>0.77678439903499485</v>
       </c>
       <c r="M263">
-        <v>4.9783980367375594E-2</v>
+        <v>4.9798061939941587E-2</v>
       </c>
       <c r="N263">
         <v>5</v>
@@ -29313,10 +29317,10 @@
         <v>960</v>
       </c>
       <c r="L264">
-        <v>11.451000000000001</v>
+        <v>7.2232382669323369</v>
       </c>
       <c r="M264">
-        <v>4.9170380491878628E-2</v>
+        <v>4.9012371554502901E-2</v>
       </c>
       <c r="N264">
         <v>1</v>
@@ -29351,10 +29355,10 @@
         <v>960</v>
       </c>
       <c r="L265">
-        <v>11.409000000000001</v>
+        <v>4.5990962494652399</v>
       </c>
       <c r="M265">
-        <v>4.8867271725558895E-2</v>
+        <v>4.887557802114504E-2</v>
       </c>
       <c r="N265">
         <v>4</v>
@@ -29389,10 +29393,10 @@
         <v>960</v>
       </c>
       <c r="L266">
-        <v>4.5067500000000003</v>
+        <v>2.0964466237334052</v>
       </c>
       <c r="M266">
-        <v>4.1731415856527627E-2</v>
+        <v>4.1789918946553928E-2</v>
       </c>
       <c r="N266">
         <v>2</v>
@@ -29427,10 +29431,10 @@
         <v>960</v>
       </c>
       <c r="L267">
-        <v>1.38825</v>
+        <v>0.54764429271174142</v>
       </c>
       <c r="M267">
-        <v>4.1713705506781586E-2</v>
+        <v>4.1706482238926361E-2</v>
       </c>
       <c r="N267">
         <v>5</v>
@@ -29465,10 +29469,10 @@
         <v>960</v>
       </c>
       <c r="L268">
-        <v>2.7607499999999998</v>
+        <v>1.1031196862009878</v>
       </c>
       <c r="M268">
-        <v>4.1584917529009446E-2</v>
+        <v>4.1540592858571992E-2</v>
       </c>
       <c r="N268">
         <v>4</v>
@@ -29503,10 +29507,10 @@
         <v>960</v>
       </c>
       <c r="L269">
-        <v>5.3940000000000001</v>
+        <v>3.2624984766803387</v>
       </c>
       <c r="M269">
-        <v>3.8829398080525192E-2</v>
+        <v>3.8797956977864041E-2</v>
       </c>
       <c r="N269">
         <v>1</v>
@@ -29541,10 +29545,10 @@
         <v>960</v>
       </c>
       <c r="L270">
-        <v>4.95</v>
+        <v>2.0244346896781611</v>
       </c>
       <c r="M270">
-        <v>3.8331321424175446E-2</v>
+        <v>3.8413761558846182E-2</v>
       </c>
       <c r="N270">
         <v>3</v>
@@ -29579,10 +29583,10 @@
         <v>960</v>
       </c>
       <c r="L271">
-        <v>0.40200000000000002</v>
+        <v>0.17232530061963627</v>
       </c>
       <c r="M271">
-        <v>3.109186263121224E-2</v>
+        <v>3.1086081750028863E-2</v>
       </c>
       <c r="N271">
         <v>5</v>
@@ -29617,13 +29621,13 @@
         <v>960</v>
       </c>
       <c r="L272">
-        <v>0.66749999999999998</v>
+        <v>0.47073770429530326</v>
       </c>
       <c r="M272">
-        <v>3.015279391032152E-2</v>
+        <v>3.0386771272731077E-2</v>
       </c>
       <c r="N272">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273" spans="2:14">
@@ -29655,13 +29659,13 @@
         <v>960</v>
       </c>
       <c r="L273">
-        <v>0.73199999999999998</v>
+        <v>0.29367918840813789</v>
       </c>
       <c r="M273">
-        <v>3.0038912889276383E-2</v>
+        <v>3.0080889392197774E-2</v>
       </c>
       <c r="N273">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="274" spans="2:14">
@@ -29693,10 +29697,10 @@
         <v>960</v>
       </c>
       <c r="L274">
-        <v>2.37975</v>
+        <v>1.1578849293272151</v>
       </c>
       <c r="M274">
-        <v>2.8967294158395454E-2</v>
+        <v>2.8874975310395044E-2</v>
       </c>
       <c r="N274">
         <v>3</v>
@@ -29731,10 +29735,10 @@
         <v>960</v>
       </c>
       <c r="L275">
-        <v>3.1305000000000001</v>
+        <v>2.6099726756032564</v>
       </c>
       <c r="M275">
-        <v>2.8088437881881423E-2</v>
+        <v>2.8109125704514102E-2</v>
       </c>
       <c r="N275">
         <v>1</v>
@@ -29769,10 +29773,10 @@
         <v>960</v>
       </c>
       <c r="L276">
-        <v>3.6480000000000001</v>
+        <v>2.9906934548729693</v>
       </c>
       <c r="M276">
-        <v>2.1537052810195821E-2</v>
+        <v>2.1408035958546401E-2</v>
       </c>
       <c r="N276">
         <v>1</v>
@@ -29807,10 +29811,10 @@
         <v>960</v>
       </c>
       <c r="L277">
-        <v>3.28125</v>
+        <v>1.5011359015681585</v>
       </c>
       <c r="M277">
-        <v>2.1173756491206029E-2</v>
+        <v>2.1148343388274295E-2</v>
       </c>
       <c r="N277">
         <v>4</v>
@@ -29845,10 +29849,10 @@
         <v>960</v>
       </c>
       <c r="L278">
-        <v>2.3879999999999999</v>
+        <v>0.87950852254309853</v>
       </c>
       <c r="M278">
-        <v>2.0744886101730323E-2</v>
+        <v>2.0748043548506765E-2</v>
       </c>
       <c r="N278">
         <v>5</v>
@@ -29883,10 +29887,10 @@
         <v>960</v>
       </c>
       <c r="L279">
-        <v>0.22650000000000001</v>
+        <v>0.17428299461371341</v>
       </c>
       <c r="M279">
-        <v>1.9220639498641102E-2</v>
+        <v>1.8572379990977311E-2</v>
       </c>
       <c r="N279">
         <v>3</v>
@@ -29921,10 +29925,10 @@
         <v>960</v>
       </c>
       <c r="L280">
-        <v>2.6265000000000001</v>
+        <v>2.0081391518271756</v>
       </c>
       <c r="M280">
-        <v>1.763205105907836E-2</v>
+        <v>1.7750701698900449E-2</v>
       </c>
       <c r="N280">
         <v>2</v>
@@ -29959,10 +29963,10 @@
         <v>960</v>
       </c>
       <c r="L281">
-        <v>5.5500000000000001E-2</v>
+        <v>5.081017119072917E-2</v>
       </c>
       <c r="M281">
-        <v>1.3958764093774159E-2</v>
+        <v>1.3969530923048909E-2</v>
       </c>
       <c r="N281">
         <v>2</v>
@@ -29997,10 +30001,10 @@
         <v>960</v>
       </c>
       <c r="L282">
-        <v>3.5999999999999997E-2</v>
+        <v>1.3356734693877553E-2</v>
       </c>
       <c r="M282">
-        <v>1.3901187234242699E-2</v>
+        <v>1.39011871734121E-2</v>
       </c>
       <c r="N282">
         <v>5</v>
@@ -30035,10 +30039,10 @@
         <v>960</v>
       </c>
       <c r="L283">
-        <v>0.11700000000000001</v>
+        <v>4.5384320381867543E-2</v>
       </c>
       <c r="M283">
-        <v>1.2553073584339065E-2</v>
+        <v>1.2552446093897395E-2</v>
       </c>
       <c r="N283">
         <v>4</v>
@@ -30073,10 +30077,10 @@
         <v>960</v>
       </c>
       <c r="L284">
-        <v>0.93</v>
+        <v>0.37885179862597768</v>
       </c>
       <c r="M284">
-        <v>1.1114692026054271E-2</v>
+        <v>1.1112022719536735E-2</v>
       </c>
       <c r="N284">
         <v>3</v>
@@ -30111,10 +30115,10 @@
         <v>960</v>
       </c>
       <c r="L285">
-        <v>1.02</v>
+        <v>0.91408008667688023</v>
       </c>
       <c r="M285">
-        <v>8.926304062786071E-3</v>
+        <v>8.9311422397310679E-3</v>
       </c>
       <c r="N285">
         <v>1</v>
@@ -30149,7 +30153,7 @@
         <v>960</v>
       </c>
       <c r="L286">
-        <v>0.48525000000000001</v>
+        <v>0.45616115894043968</v>
       </c>
       <c r="M286">
         <v>0</v>
@@ -30164,7 +30168,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EDC2F93-6AF6-47C5-8DD8-39FB6D1E9722}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E1A06B4-EC05-4C86-8773-36A140D0F20D}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC6EE8F3-35D8-4C0E-B653-F8C150FAB212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8177A302-5DD8-4A3C-919F-E61663B9D91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9012,7 +9012,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0859269-96E5-4EBF-BAB4-2C4C4F0CD346}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACB7D6FA-0B37-4A1F-8FE4-3DE98FA316B7}">
   <dimension ref="B9:N119"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13210,7 +13210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC829776-0CF7-4D84-91C6-D25659024241}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B57A7BCB-A5CF-4C11-8251-5F13ACAE7264}">
   <dimension ref="B9:AB286"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -30168,7 +30168,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E1A06B4-EC05-4C86-8773-36A140D0F20D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1293FEF-DE1A-4DDC-BA91-4A33DA661BB9}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8177A302-5DD8-4A3C-919F-E61663B9D91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C625C03D-C5E9-4D3E-A170-5057096FC93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9012,7 +9012,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACB7D6FA-0B37-4A1F-8FE4-3DE98FA316B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C6F098D-3EB2-4D69-AE85-8671E789F7C1}">
   <dimension ref="B9:N119"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13210,7 +13210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B57A7BCB-A5CF-4C11-8251-5F13ACAE7264}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E363F678-1826-457F-A250-99906835A666}">
   <dimension ref="B9:AB286"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -30168,7 +30168,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1293FEF-DE1A-4DDC-BA91-4A33DA661BB9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{443D687F-6FC1-4966-943F-1E482CC129C4}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C625C03D-C5E9-4D3E-A170-5057096FC93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{55B42716-8BEC-4C3C-9A8F-E01336B8B659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9012,7 +9012,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C6F098D-3EB2-4D69-AE85-8671E789F7C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{441C32FF-12E3-403A-9971-F3117F6DB6AB}">
   <dimension ref="B9:N119"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13210,7 +13210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E363F678-1826-457F-A250-99906835A666}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EC361C-B6E7-4394-8D16-030E86B68593}">
   <dimension ref="B9:AB286"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -30168,7 +30168,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{443D687F-6FC1-4966-943F-1E482CC129C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5BFE421-8B44-4164-9B24-2AF270F3B38C}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55B42716-8BEC-4C3C-9A8F-E01336B8B659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C2B40F8-AD15-4675-B4D2-444264F308B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9012,7 +9012,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{441C32FF-12E3-403A-9971-F3117F6DB6AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{122D0E28-339C-4116-9C6D-B5CB5D313BCC}">
   <dimension ref="B9:N119"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13210,7 +13210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EC361C-B6E7-4394-8D16-030E86B68593}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDA28D5-AEBA-4E30-92B9-4E6377B730E0}">
   <dimension ref="B9:AB286"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -30168,7 +30168,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5BFE421-8B44-4164-9B24-2AF270F3B38C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF0C83C1-0098-4EC1-BBE0-669852664F23}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C2B40F8-AD15-4675-B4D2-444264F308B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A424650-0821-4482-87C2-D5612552B0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9012,7 +9012,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{122D0E28-339C-4116-9C6D-B5CB5D313BCC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02D2FE08-FF19-4D98-A756-998968EA2AAB}">
   <dimension ref="B9:N119"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13210,7 +13210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FDA28D5-AEBA-4E30-92B9-4E6377B730E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47809E32-AE94-49A7-86D2-8828E209FC5F}">
   <dimension ref="B9:AB286"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -30168,7 +30168,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF0C83C1-0098-4EC1-BBE0-669852664F23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6A8E799-D320-4790-A6EF-39B6A78CAD8E}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A424650-0821-4482-87C2-D5612552B0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF2F7598-ACD5-4353-90BF-7BB1FBA40F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9012,7 +9012,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02D2FE08-FF19-4D98-A756-998968EA2AAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27C565D-9C46-4C96-AB1B-262FF9C7B59F}">
   <dimension ref="B9:N119"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13210,7 +13210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47809E32-AE94-49A7-86D2-8828E209FC5F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6A8BE6E-11D9-47E3-9A05-DFFE456E6A70}">
   <dimension ref="B9:AB286"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -30168,7 +30168,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6A8E799-D320-4790-A6EF-39B6A78CAD8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{174FD076-6536-4531-88AD-788454223A93}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF2F7598-ACD5-4353-90BF-7BB1FBA40F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2C55F13-C88C-4860-A62E-67F04F598537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9012,7 +9012,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27C565D-9C46-4C96-AB1B-262FF9C7B59F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{729193DB-62BC-4CA8-98C4-907448DF5F4C}">
   <dimension ref="B9:N119"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13210,7 +13210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6A8BE6E-11D9-47E3-9A05-DFFE456E6A70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66289F17-3DDD-4FEB-A0DF-EDA464CEC8EE}">
   <dimension ref="B9:AB286"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -30168,7 +30168,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{174FD076-6536-4531-88AD-788454223A93}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B94B80-9C90-49BC-8556-889A6DD8B6D7}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2C55F13-C88C-4860-A62E-67F04F598537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEBF921E-3DED-4C54-90F6-586675FE8F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9012,7 +9012,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{729193DB-62BC-4CA8-98C4-907448DF5F4C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE263B6-8BC2-405A-84E9-1FF79022630E}">
   <dimension ref="B9:N119"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13210,7 +13210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66289F17-3DDD-4FEB-A0DF-EDA464CEC8EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD6B64E-B48B-4273-8430-470E85A3AF08}">
   <dimension ref="B9:AB286"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -30168,7 +30168,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17B94B80-9C90-49BC-8556-889A6DD8B6D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FB909D-5A2E-40A8-90EC-25EE2A7D75D3}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEBF921E-3DED-4C54-90F6-586675FE8F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{15CF3FF7-15EF-406C-94C7-00F48C12A7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9012,7 +9012,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FE263B6-8BC2-405A-84E9-1FF79022630E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9079522-CDA1-4115-8F9A-35644AAEF7BD}">
   <dimension ref="B9:N119"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13210,7 +13210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD6B64E-B48B-4273-8430-470E85A3AF08}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB32582-BAF4-4A5F-A6FA-7710236181F9}">
   <dimension ref="B9:AB286"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -30168,7 +30168,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FB909D-5A2E-40A8-90EC-25EE2A7D75D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F325FB98-D846-4B45-A297-25C7FFE7AB23}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15CF3FF7-15EF-406C-94C7-00F48C12A7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4EBF827-B4A8-4D2F-9273-BB9F4669C069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9012,7 +9012,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9079522-CDA1-4115-8F9A-35644AAEF7BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A23D24-ECB4-496A-92A4-E76FBA59BD61}">
   <dimension ref="B9:N119"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13210,7 +13210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DB32582-BAF4-4A5F-A6FA-7710236181F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B4280A-73B6-4F52-AD1C-9E822C7497DE}">
   <dimension ref="B9:AB286"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -30168,7 +30168,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F325FB98-D846-4B45-A297-25C7FFE7AB23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24D5CD1C-EB56-449B-927E-8CBCD4EBAC26}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_USA/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_USA\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F048C176-9281-4305-A735-BB6B13E6031A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E62926E1-F18A-4A5D-B234-27296B0A884A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8029,7 +8029,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D835E673-FE28-433A-BC22-0C405F9844E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34A7C41C-69E5-4E90-82FC-33F523541089}">
   <dimension ref="B9:M149"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12947,7 +12947,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA974EC9-0E51-4966-8B9D-AF61D86B916B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE8DB4D0-A55F-4D31-AC92-792DCE16E7EB}">
   <dimension ref="B9:Z140"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -18084,7 +18084,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85C35F28-2460-44B9-97B0-96ADB07F3396}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2AB38A6-DBF1-477C-B745-8C7A16C4C76D}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
